--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="M32" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="N32" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>6.64</v>
+        <v>4.32</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="M35" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB35" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M37" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N39" t="n">
-        <v>2.37</v>
+        <v>6.83</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI45"/>
+  <dimension ref="A1:AI48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46092.61458333334</v>
+        <v>46092.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,80 +3273,80 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.25</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
         <v>4</v>
       </c>
-      <c r="N24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46092.61458333334</v>
+        <v>46092.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46092.625</v>
+        <v>46092.60416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46092.66666666666</v>
+        <v>46092.61458333334</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46092.66666666666</v>
+        <v>46092.61458333334</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46092.66666666666</v>
+        <v>46092.625</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46092.6875</v>
+        <v>46092.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46092.6875</v>
+        <v>46092.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.6875</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.6875</v>
       </c>
     </row>
     <row r="34">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>6.64</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>4.32</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.75</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.37</v>
+        <v>6.64</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="M38" t="n">
-        <v>3.9</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="39">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>2.69</v>
       </c>
       <c r="M39" t="n">
-        <v>4.95</v>
+        <v>3.48</v>
       </c>
       <c r="N39" t="n">
-        <v>6.83</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,16 +5107,16 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="40">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5259,27 +5259,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,14 +5300,14 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N41" t="n">
         <v>2.5</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.89</v>
-      </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46092.79166666666</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="42">
@@ -5378,27 +5378,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>3.68</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46092.79166666666</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="43">
@@ -5497,27 +5497,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>5.66</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46092.83333333334</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="44">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>4.04</v>
+        <v>3.38</v>
       </c>
       <c r="N44" t="n">
-        <v>5.25</v>
+        <v>2.89</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46092.89583333334</v>
+        <v>46092.79166666666</v>
       </c>
     </row>
     <row r="45">
@@ -5735,116 +5735,473 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>46092.79166666666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3" t="n">
+        <v>46092.83333333334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>46092.89583333334</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>Corinthians</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="L48" t="n">
         <v>1.6</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M48" t="n">
         <v>3.91</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N48" t="n">
         <v>6.27</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AB48" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" s="3" t="n">
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N36" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>6.64</v>
+        <v>4.32</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="N38" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.69</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
-        <v>3.48</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>6.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>4.32</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>4.32</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.69</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>3.48</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>6.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>6.64</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="M35" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB35" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>6.64</v>
+        <v>4.32</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
         <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M47" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N47" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N48" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>6.64</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>6.64</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="M36" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M44" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N44" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>4.32</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.43</v>
+        <v>2.69</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>3.48</v>
       </c>
       <c r="N35" t="n">
-        <v>6.64</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>6.64</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>4.32</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>6.83</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
         <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
         <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N44" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N34" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>6.64</v>
+        <v>4.32</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>6.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="M39" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB39" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
         <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M47" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N47" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M48" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N48" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI48"/>
+  <dimension ref="A1:AI49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB34" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N36" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>4.32</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.48</v>
       </c>
       <c r="N38" t="n">
-        <v>6.64</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>6.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,76 +5181,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="41">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5616,27 +5616,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3.38</v>
+        <v>4.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2.89</v>
+        <v>6.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46092.79166666666</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="45">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="N46" t="n">
-        <v>5.66</v>
+        <v>3.68</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
         <v>1.68</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46092.83333333334</v>
+        <v>46092.79166666666</v>
       </c>
     </row>
     <row r="47">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>4.04</v>
+        <v>3.62</v>
       </c>
       <c r="N47" t="n">
-        <v>5.25</v>
+        <v>5.66</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46092.89583333334</v>
+        <v>46092.83333333334</v>
       </c>
     </row>
     <row r="48">
@@ -6202,6 +6202,125 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
+        <v>46092.89583333334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
         <v>46092.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.83</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>6.64</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB36" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>4.32</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>4.32</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>6.64</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5187,67 +5187,67 @@
         <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>6.83</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N48" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N49" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N34" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.83</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>4.32</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>2.69</v>
       </c>
       <c r="M36" t="n">
-        <v>4.6</v>
+        <v>3.48</v>
       </c>
       <c r="N36" t="n">
-        <v>6.64</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>6.64</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>4.32</v>
+        <v>2.43</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
         <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M48" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N48" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M49" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N49" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>4.32</v>
+        <v>2.55</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="M36" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="N38" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>4.32</v>
       </c>
       <c r="O39" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
         <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N48" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N49" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -3035,7 +3035,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>6.83</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M48" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N48" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M49" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N49" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4592,67 +4592,67 @@
         <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>6.64</v>
+        <v>4.32</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>6.83</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
         <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
         <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N48" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N49" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46092.4375</v>
+        <v>46092.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46092.45833333334</v>
+        <v>46092.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46092.45833333334</v>
+        <v>46092.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46092.45833333334</v>
+        <v>46092.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46092.45833333334</v>
+        <v>46092.47916666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46092.47916666666</v>
+        <v>46092.48958333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46092.48958333334</v>
+        <v>46092.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>6.64</v>
       </c>
       <c r="O36" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>6.64</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>4.32</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>6.64</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="M40" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>6.83</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>6.83</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N35" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>4.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>6.64</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M48" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N48" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M49" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N49" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -698,34 +698,34 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.83</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>6.64</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB34" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>6.64</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="M38" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="N38" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
         <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M43" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N48" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N49" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>9.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
         <v>3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46092.33333333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>2.75</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46092.58333333334</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>6.64</v>
+        <v>2.55</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N36" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N37" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.83</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.45</v>
+        <v>6.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB38" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="M39" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>4.32</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
         <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1.18</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>9.75</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="W2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.15</v>
       </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Z2" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>9.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N34" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="O34" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
         <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.83</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S36" t="n">
         <v>3.22</v>
       </c>
-      <c r="N36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB36" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>4.32</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA37" t="n">
         <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>6.64</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N40" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N41" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>6.83</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,49 +5538,49 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M43" t="n">
         <v>3.7</v>
       </c>
       <c r="N43" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q43" t="n">
         <v>2.5</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA43" t="n">
         <v>1.57</v>
@@ -5589,22 +5589,22 @@
         <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,49 +5657,49 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA44" t="n">
         <v>1.57</v>
@@ -5708,22 +5708,22 @@
         <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M48" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N48" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M49" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N49" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46092.4375</v>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="T35" t="n">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
-        <v>5.85</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.86</v>
+        <v>2.76</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,49 +4705,49 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>2.63</v>
       </c>
       <c r="M36" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>6.64</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
-        <v>1.92</v>
+        <v>2.85</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="AA36" t="n">
         <v>1.63</v>
@@ -4756,22 +4756,22 @@
         <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.73</v>
+        <v>1.56</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>6.64</v>
       </c>
       <c r="O38" t="n">
-        <v>3.17</v>
+        <v>1.92</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.87</v>
+        <v>6.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="U38" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.41</v>
+        <v>4.15</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>2.73</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AA40" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>6.83</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>6.83</v>
       </c>
       <c r="O42" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,49 +5538,49 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
         <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="P43" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
         <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U43" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="W43" t="n">
         <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA43" t="n">
         <v>1.57</v>
@@ -5589,22 +5589,22 @@
         <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AE43" t="n">
         <v>1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="N48" t="n">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.04</v>
+        <v>3.91</v>
       </c>
       <c r="N49" t="n">
-        <v>5.25</v>
+        <v>6.27</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46092.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.69</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
-        <v>3.48</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.42</v>
+        <v>6.64</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="P34" t="n">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U34" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.46</v>
+        <v>2.73</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.83</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.42</v>
+        <v>2.06</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S36" t="n">
         <v>2.85</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.46</v>
       </c>
-      <c r="V36" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>4.32</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.29</v>
+        <v>2.77</v>
       </c>
       <c r="P37" t="n">
         <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.1</v>
+        <v>3.79</v>
       </c>
       <c r="R37" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AF37" t="n">
         <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>6.64</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
-        <v>1.92</v>
+        <v>3.17</v>
       </c>
       <c r="P38" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.1</v>
+        <v>2.87</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="T38" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V38" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.15</v>
+        <v>3.41</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.73</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.79</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.35</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.36</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V40" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
+      <c r="AE40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>6.83</v>
+        <v>4.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>6.83</v>
       </c>
       <c r="O44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>6.64</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.92</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="AG34" t="n">
         <v>1.3</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH34" t="n">
-        <v>2.73</v>
+        <v>1.39</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.35</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V35" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH35" t="n">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.69</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>3.48</v>
+        <v>4.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>6.64</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="P36" t="n">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.46</v>
+        <v>2.73</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>4.32</v>
       </c>
       <c r="O37" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="P37" t="n">
         <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.79</v>
+        <v>5.1</v>
       </c>
       <c r="R37" t="n">
         <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="T37" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AF37" t="n">
         <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
         <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="T38" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="M39" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>2.79</v>
       </c>
       <c r="P39" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>3.91</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U39" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V39" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,49 +5300,49 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
         <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="P41" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U41" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="V41" t="n">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="W41" t="n">
         <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
@@ -5351,22 +5351,22 @@
         <v>2.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AE41" t="n">
         <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,40 +5419,40 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P42" t="n">
         <v>2.36</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.42</v>
-      </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V42" t="n">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
@@ -5461,7 +5461,7 @@
         <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
@@ -5470,22 +5470,22 @@
         <v>2.37</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.01</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,49 +5538,49 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>2.36</v>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
         <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA43" t="n">
         <v>1.57</v>
@@ -5589,22 +5589,22 @@
         <v>2.37</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.54</v>
+        <v>2.01</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF46" t="n">
         <v>2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6017,70 +6017,70 @@
         <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>5.66</v>
+        <v>4.33</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH47" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46092.83333333334</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="M48" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46092.89583333334</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.65</v>
+        <v>12.46</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>5.75</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>9.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.17</v>
+        <v>3.68</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.17</v>
+        <v>2.59</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.32</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>9.75</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.86</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.21</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -942,10 +942,10 @@
         <v>2.59</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
         <v>3.6</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>2.02</v>
@@ -2819,22 +2819,22 @@
         <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="T20" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
@@ -2843,31 +2843,31 @@
         <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
         <v>1.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46092.58333333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U34" t="n">
         <v>1.4</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>6.65</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="R35" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4708,10 +4708,10 @@
         <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="N36" t="n">
-        <v>6.64</v>
+        <v>6.62</v>
       </c>
       <c r="O36" t="n">
         <v>1.92</v>
@@ -4744,19 +4744,19 @@
         <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
         <v>4.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AD36" t="n">
         <v>1.42</v>
@@ -4827,10 +4827,10 @@
         <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>2.29</v>
@@ -4860,7 +4860,7 @@
         <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
         <v>1.25</v>
@@ -4869,10 +4869,10 @@
         <v>3.72</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC37" t="n">
         <v>2.83</v>
@@ -4881,16 +4881,16 @@
         <v>1.33</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
         <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="M38" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V38" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.36</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5071,64 +5071,64 @@
         <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="P39" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T39" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U39" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W39" t="n">
         <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AA39" t="n">
         <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC39" t="n">
         <v>3.24</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="V40" t="n">
-        <v>5.85</v>
+        <v>8.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.86</v>
+        <v>2.95</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.5</v>
       </c>
-      <c r="O41" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.05</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="W41" t="n">
         <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE41" t="n">
         <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,40 +5419,40 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
         <v>2.37</v>
       </c>
       <c r="O42" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="P42" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
@@ -5461,31 +5461,31 @@
         <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,40 +5538,40 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>6.15</v>
       </c>
       <c r="O43" t="n">
-        <v>2.36</v>
+        <v>1.93</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T43" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
         <v>1.02</v>
@@ -5580,31 +5580,31 @@
         <v>1.18</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.01</v>
+        <v>2.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>6.83</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF45" t="n">
         <v>2</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.79166666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
         <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T34" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V34" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z34" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,22 +4586,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="M35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.3</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O35" t="n">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.09</v>
+        <v>3.95</v>
       </c>
       <c r="R35" t="n">
         <v>1.4</v>
@@ -4610,49 +4610,49 @@
         <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC35" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.43</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="N36" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V36" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.15</v>
+        <v>3.72</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.51</v>
+        <v>2.83</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.73</v>
+        <v>2.07</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>6.62</v>
       </c>
       <c r="O37" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="P37" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.72</v>
+        <v>4.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.07</v>
+        <v>2.73</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
         <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.4</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V39" t="n">
-        <v>7.1</v>
+        <v>6.65</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AG39" t="n">
         <v>1.31</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="P42" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="U42" t="n">
         <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="W42" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
         <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,40 +5538,40 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>6.15</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
-        <v>1.93</v>
+        <v>3.08</v>
       </c>
       <c r="P43" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="R43" t="n">
         <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X43" t="n">
         <v>1.02</v>
@@ -5580,31 +5580,31 @@
         <v>1.18</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.06</v>
+        <v>2.63</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.64</v>
+        <v>1.54</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>6.15</v>
       </c>
       <c r="O44" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T44" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V44" t="n">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="W44" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
         <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH44" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.79166666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF46" t="n">
         <v>2</v>
       </c>
-      <c r="AB46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
         <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="T48" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="U48" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V48" t="n">
-        <v>7.5</v>
+        <v>6.85</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG48" t="n">
         <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
         <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="P49" t="n">
         <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S49" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T49" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U49" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V49" t="n">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X49" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46092.89583333334</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
         <v>3.65</v>
@@ -820,7 +820,7 @@
         <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.45</v>
+        <v>4.54</v>
       </c>
       <c r="AA3" t="n">
         <v>1.58</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
         <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="O10" t="n">
         <v>2.25</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.77</v>
       </c>
       <c r="O20" t="n">
         <v>2.02</v>
@@ -2822,7 +2822,7 @@
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="T20" t="n">
         <v>2.18</v>
@@ -2831,7 +2831,7 @@
         <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
@@ -2843,7 +2843,7 @@
         <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
       <c r="AA20" t="n">
         <v>1.52</v>
@@ -2858,16 +2858,16 @@
         <v>1.56</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AG20" t="n">
         <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46092.58333333334</v>
@@ -4467,19 +4467,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
         <v>3.09</v>
@@ -4595,13 +4595,13 @@
         <v>3.3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="R35" t="n">
         <v>1.4</v>
@@ -4646,13 +4646,13 @@
         <v>1.74</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG35" t="n">
         <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12.46</v>
+        <v>3.5</v>
       </c>
       <c r="M2" t="n">
-        <v>5.75</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1.18</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>9.75</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.86</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.25</v>
+        <v>4.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>1.52</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.69</v>
+        <v>2.34</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.5</v>
+        <v>12.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>5.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>9.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="T3" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.54</v>
+        <v>5.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2563,22 +2563,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="O18" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="R18" t="n">
         <v>1.24</v>
@@ -2608,7 +2608,7 @@
         <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
         <v>2.21</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3039,16 +3039,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
@@ -3057,55 +3057,55 @@
         <v>8.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
         <v>3.32</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
         <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.54</v>
+        <v>4.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF34" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.19</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
-        <v>2.84</v>
+        <v>3.64</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.93</v>
+        <v>3.09</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V35" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="AD35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="O36" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U36" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
-        <v>6.45</v>
+        <v>7.1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.83</v>
+        <v>3.46</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>2.36</v>
       </c>
       <c r="M37" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>6.62</v>
+        <v>2.71</v>
       </c>
       <c r="O37" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.1</v>
+        <v>3.28</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="U37" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V37" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.73</v>
+        <v>1.54</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="O38" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.32</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.46</v>
-      </c>
       <c r="V38" t="n">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
         <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>4.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH39" t="n">
         <v>2.06</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="P40" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.47</v>
+        <v>3.22</v>
       </c>
       <c r="T40" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="U40" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
         <v>1.03</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y40" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.95</v>
+        <v>4.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.7</v>
+        <v>2.51</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O41" t="n">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="P41" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="M42" t="n">
         <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>2.35</v>
+        <v>3.84</v>
       </c>
       <c r="P42" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V42" t="n">
-        <v>5.45</v>
+        <v>5.1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AH42" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="P43" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
         <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="U43" t="n">
         <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="W43" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
         <v>1.18</v>
       </c>
       <c r="Z43" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA43" t="n">
         <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5657,31 +5657,31 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="N44" t="n">
         <v>6.15</v>
       </c>
       <c r="O44" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="T44" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="U44" t="n">
         <v>1.58</v>
@@ -5690,28 +5690,28 @@
         <v>4.95</v>
       </c>
       <c r="W44" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
         <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AB44" t="n">
         <v>2.27</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE44" t="n">
         <v>1.68</v>
@@ -5720,10 +5720,10 @@
         <v>2.06</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.79166666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N47" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="O47" t="n">
         <v>2.25</v>
@@ -6041,7 +6041,7 @@
         <v>2.81</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V47" t="n">
         <v>6.05</v>
@@ -6050,19 +6050,19 @@
         <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
         <v>3.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC47" t="n">
         <v>3.55</v>
@@ -6151,7 +6151,7 @@
         <v>6.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
         <v>3.04</v>
@@ -6160,16 +6160,16 @@
         <v>2.6</v>
       </c>
       <c r="U48" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V48" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
         <v>1.25</v>
@@ -6178,7 +6178,7 @@
         <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB48" t="n">
         <v>1.85</v>
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M49" t="n">
         <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="O49" t="n">
         <v>2.19</v>
@@ -6270,31 +6270,31 @@
         <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="T49" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
         <v>1.34</v>
       </c>
       <c r="V49" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
         <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AA49" t="n">
         <v>2.1</v>
@@ -6306,13 +6306,13 @@
         <v>3.82</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE49" t="n">
         <v>2.04</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -677,7 +677,7 @@
         <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -689,7 +689,7 @@
         <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -701,7 +701,7 @@
         <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="AA2" t="n">
         <v>1.58</v>
@@ -710,16 +710,16 @@
         <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="n">
         <v>1.52</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
         <v>1.21</v>
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12.46</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="T3" t="n">
         <v>2.08</v>
@@ -808,7 +808,7 @@
         <v>1.66</v>
       </c>
       <c r="V3" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="W3" t="n">
         <v>1.15</v>
@@ -817,31 +817,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AC3" t="n">
         <v>2.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
         <v>1.04</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -2328,10 +2328,10 @@
         <v>2.42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2807,7 +2807,7 @@
         <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>2.02</v>
@@ -2840,22 +2840,22 @@
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.97</v>
+        <v>4.1</v>
       </c>
       <c r="AA20" t="n">
         <v>1.52</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>2.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
         <v>1.49</v>
@@ -2864,10 +2864,10 @@
         <v>2.42</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46092.58333333334</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>1.96</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>3.84</v>
+        <v>2.56</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.53</v>
+        <v>4.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46092.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46092.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46092.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.64</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
         <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.16</v>
+        <v>4.03</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z34" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="O35" t="n">
-        <v>3.64</v>
+        <v>2.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="U35" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD35" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE35" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.19</v>
+        <v>2.66</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="T36" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="V36" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X36" t="n">
         <v>1.04</v>
       </c>
-      <c r="X36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.36</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="N37" t="n">
-        <v>2.71</v>
+        <v>6.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.28</v>
+        <v>6.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="T37" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.82</v>
+        <v>4.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.54</v>
+        <v>2.73</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="T38" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V38" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W38" t="n">
         <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.44</v>
+        <v>2.64</v>
       </c>
       <c r="M40" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AA40" t="n">
         <v>1.92</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AB40" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.51</v>
+        <v>3.05</v>
       </c>
       <c r="AD40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>2.73</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
         <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.84</v>
+        <v>2.35</v>
       </c>
       <c r="P42" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U42" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="M43" t="n">
         <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>2.35</v>
+        <v>3.84</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
         <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V43" t="n">
-        <v>5.45</v>
+        <v>5.1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA43" t="n">
         <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AH43" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.79166666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="O48" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
         <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="T48" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V48" t="n">
         <v>6.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AG48" t="n">
         <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="P49" t="n">
         <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R49" t="n">
         <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U49" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V49" t="n">
         <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46092.89583333334</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z2" t="n">
         <v>5.2</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.52</v>
+        <v>2.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46092.4375</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M18" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.56</v>
+        <v>3.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.08</v>
+        <v>2.52</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.72</v>
+        <v>4.13</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46092.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>3.26</v>
+        <v>2.56</v>
       </c>
       <c r="P30" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52</v>
+        <v>4.08</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="W30" t="n">
         <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="O34" t="n">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.03</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.4</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V34" t="n">
-        <v>6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z34" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="T35" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U35" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N36" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S36" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="U36" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.95</v>
+        <v>3.82</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.92</v>
+        <v>2.79</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.1</v>
+        <v>4.03</v>
       </c>
       <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.3</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.73</v>
+        <v>1.65</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,22 +4943,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
-        <v>3.64</v>
+        <v>2.34</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="R38" t="n">
         <v>1.4</v>
@@ -4967,49 +4967,49 @@
         <v>2.73</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U38" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="N39" t="n">
-        <v>4.65</v>
+        <v>6.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.05</v>
+        <v>6.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="T39" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V39" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB39" t="n">
         <v>1.99</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.06</v>
+        <v>2.84</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T40" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V40" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.37</v>
+        <v>2.02</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U41" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="W41" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF41" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,25 +5419,25 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="O42" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="P42" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
         <v>3.5</v>
@@ -5449,43 +5449,43 @@
         <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>5.45</v>
+        <v>4.75</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
         <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3.84</v>
+        <v>1.9</v>
       </c>
       <c r="P43" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="W43" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
         <v>1.02</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z43" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>2.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,37 +5657,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="N44" t="n">
-        <v>6.15</v>
+        <v>3.9</v>
       </c>
       <c r="O44" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="P44" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="R44" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U44" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="W44" t="n">
         <v>1.13</v>
@@ -5696,34 +5696,34 @@
         <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.79166666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R48" t="n">
         <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U48" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V48" t="n">
         <v>6.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG48" t="n">
         <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="O49" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="P49" t="n">
         <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
         <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="T49" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V49" t="n">
         <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46092.89583333334</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M19" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46092.54166666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>3.26</v>
+        <v>2.56</v>
       </c>
       <c r="P29" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.52</v>
+        <v>4.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46092.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>5.34</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.28</v>
+        <v>2.54</v>
       </c>
       <c r="R32" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE32" t="n">
         <v>2.14</v>
       </c>
-      <c r="T32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V32" t="n">
-        <v>13</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46092.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>5.34</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.54</v>
+        <v>4.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="S33" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="T33" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="U33" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V33" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.41</v>
+        <v>2.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.81</v>
+        <v>5.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46092.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="O34" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V34" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
         <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.08</v>
+        <v>4.03</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V35" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.99</v>
+        <v>3.46</v>
       </c>
       <c r="AD35" t="n">
         <v>1.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>2.95</v>
+        <v>3.64</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T36" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="V36" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.03</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.4</v>
       </c>
-      <c r="S37" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V37" t="n">
-        <v>6</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.4</v>
       </c>
-      <c r="M39" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="N39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="V39" t="n">
         <v>6.1</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC39" t="n">
         <v>2.99</v>
       </c>
-      <c r="T39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V39" t="n">
-        <v>6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AD39" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.84</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.64</v>
+        <v>1.9</v>
       </c>
       <c r="P40" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.05</v>
+        <v>6.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S40" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="T40" t="n">
         <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.99</v>
+        <v>3.76</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.54</v>
+        <v>3.14</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.39</v>
+        <v>2.84</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,22 +5419,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="P42" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="R42" t="n">
         <v>1.28</v>
@@ -5443,49 +5443,49 @@
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
         <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="W42" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA42" t="n">
         <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,22 +5657,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="O44" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="R44" t="n">
         <v>1.28</v>
@@ -5681,49 +5681,49 @@
         <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U44" t="n">
         <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="W44" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X44" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA44" t="n">
         <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH44" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.79166666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="O48" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
         <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="T48" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V48" t="n">
         <v>6.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AG48" t="n">
         <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="P49" t="n">
         <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R49" t="n">
         <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U49" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V49" t="n">
         <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46092.89583333334</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>1.19</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z3" t="n">
         <v>5.2</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.52</v>
+        <v>2.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M18" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46092.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
-        <v>3.26</v>
+        <v>2.56</v>
       </c>
       <c r="P31" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>4.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="W31" t="n">
         <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.18</v>
+        <v>5.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T34" t="n">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U34" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.82</v>
+        <v>3.24</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
         <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="O35" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.03</v>
+        <v>3.18</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="U35" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X35" t="n">
         <v>1.04</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
-        <v>3.64</v>
+        <v>1.9</v>
       </c>
       <c r="P36" t="n">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.05</v>
+        <v>6.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="T36" t="n">
         <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.99</v>
+        <v>3.76</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.54</v>
+        <v>3.14</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.39</v>
+        <v>2.84</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.75</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W37" t="n">
         <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,22 +4943,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
-        <v>2.34</v>
+        <v>2.79</v>
       </c>
       <c r="P38" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.2</v>
+        <v>4.03</v>
       </c>
       <c r="R38" t="n">
         <v>1.4</v>
@@ -4973,43 +4973,43 @@
         <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
         <v>1.83</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.4</v>
       </c>
-      <c r="M40" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="N40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="Z40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.42</v>
-      </c>
-      <c r="V40" t="n">
-        <v>6</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>2.84</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,22 +5300,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.02</v>
+        <v>2.67</v>
       </c>
       <c r="O41" t="n">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="P41" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="R41" t="n">
         <v>1.28</v>
@@ -5324,49 +5324,49 @@
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="U41" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V41" t="n">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N42" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="O42" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="P42" t="n">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T42" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V42" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB42" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC42" t="n">
         <v>2.28</v>
       </c>
-      <c r="AC42" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AD42" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH42" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="M43" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="P43" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD43" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.55</v>
       </c>
-      <c r="AE43" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AF43" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,22 +5657,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>2.67</v>
+        <v>2.02</v>
       </c>
       <c r="O44" t="n">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="P44" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="R44" t="n">
         <v>1.28</v>
@@ -5681,49 +5681,49 @@
         <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V44" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X44" t="n">
         <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA44" t="n">
         <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE44" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF44" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5898,7 +5898,7 @@
         <v>2.05</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N46" t="n">
         <v>3.6</v>
@@ -5916,7 +5916,7 @@
         <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="T46" t="n">
         <v>2.73</v>
@@ -5925,13 +5925,13 @@
         <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
         <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
         <v>1.29</v>
@@ -5943,22 +5943,22 @@
         <v>2.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
         <v>3.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF46" t="n">
         <v>2.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
         <v>1.75</v>
@@ -6017,7 +6017,7 @@
         <v>1.74</v>
       </c>
       <c r="M47" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="N47" t="n">
         <v>4.35</v>
@@ -6038,34 +6038,34 @@
         <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U47" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z47" t="n">
         <v>3.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="AD47" t="n">
         <v>1.33</v>
@@ -6077,7 +6077,7 @@
         <v>1.95</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH47" t="n">
         <v>2.05</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="N48" t="n">
-        <v>5.91</v>
+        <v>6.65</v>
       </c>
       <c r="O48" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U48" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V48" t="n">
         <v>6.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z48" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE48" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
         <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46092.89583333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,70 +6252,70 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N49" t="n">
         <v>6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="P49" t="n">
         <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S49" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T49" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U49" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH49" t="n">
         <v>2.4</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.15</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z2" t="n">
         <v>5.2</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -945,7 +945,7 @@
         <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
         <v>3.6</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46092.4375</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.05</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46092.54166666666</v>
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
         <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="T20" t="n">
         <v>2.18</v>
@@ -2831,7 +2831,7 @@
         <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.11</v>
@@ -2843,19 +2843,19 @@
         <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AC20" t="n">
         <v>2.32</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AE20" t="n">
         <v>1.49</v>
@@ -2864,10 +2864,10 @@
         <v>2.42</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46092.58333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3515,31 +3515,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="M26" t="n">
         <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O26" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R26" t="n">
         <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
         <v>1.48</v>
@@ -3554,34 +3554,34 @@
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z26" t="n">
         <v>3.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="AD26" t="n">
         <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46092.61458333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46092.66666666666</v>
@@ -3994,28 +3994,28 @@
         <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O30" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
         <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
         <v>1.48</v>
@@ -4027,19 +4027,19 @@
         <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
         <v>1.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AC30" t="n">
         <v>2.6</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>5.34</v>
+        <v>3.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.54</v>
+        <v>4.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="S32" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="T32" t="n">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V32" t="n">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.41</v>
+        <v>2.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.81</v>
+        <v>6.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46092.6875</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>5.34</v>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.28</v>
+        <v>2.54</v>
       </c>
       <c r="R33" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="S33" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.14</v>
+        <v>2.43</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46092.6875</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="T35" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U35" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>5.95</v>
+        <v>6.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R36" t="n">
         <v>1.4</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="N36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S36" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="T36" t="n">
         <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V36" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.76</v>
+        <v>2.99</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.14</v>
+        <v>3.54</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.84</v>
+        <v>1.39</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46092.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
         <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.75</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.73</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V39" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="M40" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="P40" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R40" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="U40" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V40" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
         <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,22 +5300,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>3.49</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="P41" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
         <v>1.28</v>
@@ -5324,16 +5324,16 @@
         <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
@@ -5342,31 +5342,31 @@
         <v>1.18</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF41" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="M42" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>6.5</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
-        <v>1.9</v>
+        <v>3.08</v>
       </c>
       <c r="P42" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.3</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
         <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="U42" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V42" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.85</v>
+        <v>5.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.55</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH42" t="n">
-        <v>2.64</v>
+        <v>1.47</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="O43" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="W43" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB43" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC43" t="n">
         <v>2.28</v>
       </c>
-      <c r="AC43" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AD43" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,22 +5657,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.4</v>
+        <v>1.89</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="N44" t="n">
-        <v>2.02</v>
+        <v>4.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="R44" t="n">
         <v>1.28</v>
@@ -5681,49 +5681,49 @@
         <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U44" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="V44" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X44" t="n">
         <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA44" t="n">
         <v>1.57</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.84</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.33</v>
+        <v>1.99</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46092.70833333334</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,70 +6133,70 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="M48" t="n">
-        <v>4.16</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>6.65</v>
+        <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="P48" t="n">
         <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T48" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U48" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V48" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X48" t="n">
         <v>1.04</v>
       </c>
-      <c r="X48" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y48" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH48" t="n">
         <v>2.4</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,70 +6252,70 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="O49" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="P49" t="n">
         <v>2.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="T49" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="U49" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V49" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
         <v>2.4</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI49"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,7 +689,7 @@
         <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
@@ -713,10 +713,10 @@
         <v>2.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
         <v>1.7</v>
@@ -817,7 +817,7 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
         <v>4.45</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46092.4375</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46092.4375</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="N18" t="n">
         <v>2.9</v>
@@ -2626,7 +2626,7 @@
         <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
         <v>1.63</v>
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,76 +3872,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46092.66666666666</v>
+        <v>46092.625</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46092.66666666666</v>
+        <v>46092.625</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46092.66666666666</v>
+        <v>46092.625</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4238,67 +4238,67 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46092.6875</v>
+        <v>46092.625</v>
       </c>
     </row>
     <row r="33">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,76 +4348,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.25</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>5.34</v>
+        <v>2.55</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.54</v>
+        <v>3.98</v>
       </c>
       <c r="R33" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="T33" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.25</v>
       </c>
-      <c r="V33" t="n">
-        <v>10</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>1.63</v>
       </c>
-      <c r="AG33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI33" s="3" t="n">
-        <v>46092.6875</v>
+        <v>46092.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,76 +4467,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>1.98</v>
       </c>
       <c r="O34" t="n">
-        <v>2.34</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.04</v>
+        <v>1.26</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,76 +4586,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,76 +4705,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>4.25</v>
       </c>
       <c r="M36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.3</v>
       </c>
-      <c r="N36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.99</v>
+        <v>2.43</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.6875</v>
       </c>
     </row>
     <row r="37">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,76 +4824,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P37" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4.28</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="S37" t="n">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="T37" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.7</v>
+        <v>6.34</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46092.69791666666</v>
+        <v>46092.6875</v>
       </c>
     </row>
     <row r="38">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.03</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X38" t="n">
         <v>1.04</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.4</v>
+        <v>2.95</v>
       </c>
       <c r="M39" t="n">
-        <v>4.55</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>6.5</v>
+        <v>2.41</v>
       </c>
       <c r="O39" t="n">
-        <v>1.9</v>
+        <v>3.83</v>
       </c>
       <c r="P39" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.1</v>
+        <v>3.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="S39" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="T39" t="n">
         <v>2.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.76</v>
+        <v>2.94</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.14</v>
+        <v>4.08</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.84</v>
+        <v>1.38</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="O40" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V40" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.88</v>
+        <v>3.46</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,76 +5300,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.49</v>
+        <v>2.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="P41" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="R41" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="U41" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="V41" t="n">
-        <v>5.05</v>
+        <v>6.25</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.31</v>
+        <v>2.99</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="42">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,76 +5419,76 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.05</v>
+        <v>5.25</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T42" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="43">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,76 +5538,76 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="N43" t="n">
-        <v>6.5</v>
+        <v>7.88</v>
       </c>
       <c r="O43" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P43" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="T43" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="V43" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,76 +5657,76 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.89</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="O44" t="n">
-        <v>2.32</v>
+        <v>3.48</v>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="T44" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="U44" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46092.70833333334</v>
+        <v>46092.69791666666</v>
       </c>
     </row>
     <row r="45">
@@ -5735,27 +5735,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,76 +5776,76 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P45" t="n">
         <v>2.5</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF45" t="n">
         <v>2</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46092.79166666666</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="46">
@@ -5854,27 +5854,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,76 +5895,76 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.05</v>
+        <v>3.49</v>
       </c>
       <c r="M46" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="N46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
         <v>3.6</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.45</v>
-      </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="V46" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46092.79166666666</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="47">
@@ -5973,27 +5973,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,76 +6014,76 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>4.35</v>
+        <v>2.37</v>
       </c>
       <c r="O47" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="P47" t="n">
         <v>2.25</v>
       </c>
-      <c r="P47" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q47" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="U47" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X47" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46092.83333333334</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -6092,27 +6092,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,76 +6133,76 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V48" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.56</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N48" t="n">
-        <v>6</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>6</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE48" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46092.89583333334</v>
+        <v>46092.70833333334</v>
       </c>
     </row>
     <row r="49">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,75 +6252,551 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="M49" t="n">
-        <v>4.16</v>
+        <v>3.42</v>
       </c>
       <c r="N49" t="n">
-        <v>6.65</v>
+        <v>3.6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="P49" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T49" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U49" t="n">
         <v>1.4</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB49" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AC49" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>
       </c>
       <c r="AH49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>46092.79166666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
+        <v>46092.79166666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>46092.83333333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH52" t="n">
         <v>2.4</v>
       </c>
-      <c r="AI49" s="3" t="n">
+      <c r="AI52" s="3" t="n">
+        <v>46092.89583333334</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI53" s="3" t="n">
         <v>46092.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.21</v>
       </c>
-      <c r="S2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46092.3125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z3" t="n">
         <v>5.2</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46092.3125</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1263,64 +1263,64 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46092.41666666666</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46092.60416666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="O33" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.98</v>
+        <v>2.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V33" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="W33" t="n">
         <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.1</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.98</v>
-      </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>3.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V34" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46092.66666666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="P38" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="T38" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.76</v>
+        <v>3.46</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>2.41</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3.83</v>
+        <v>2.3</v>
       </c>
       <c r="P39" t="n">
         <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.08</v>
+        <v>5.25</v>
       </c>
       <c r="R39" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S39" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="W39" t="n">
         <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE39" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
         <v>2.19</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U40" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V40" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="W40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X40" t="n">
         <v>1.04</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.46</v>
+        <v>2.76</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.67</v>
+        <v>1.46</v>
       </c>
       <c r="M41" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.04</v>
+        <v>1.85</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.08</v>
+        <v>6.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="T41" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V41" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W41" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.43</v>
+        <v>2.93</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,22 +5419,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>2.68</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="R42" t="n">
         <v>1.39</v>
@@ -5443,49 +5443,49 @@
         <v>2.77</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U42" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V42" t="n">
-        <v>7.4</v>
+        <v>6.25</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>2.95</v>
       </c>
       <c r="M43" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="N43" t="n">
-        <v>7.88</v>
+        <v>2.41</v>
       </c>
       <c r="O43" t="n">
-        <v>1.85</v>
+        <v>3.83</v>
       </c>
       <c r="P43" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.1</v>
+        <v>3.08</v>
       </c>
       <c r="R43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.3</v>
       </c>
-      <c r="S43" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V43" t="n">
-        <v>6</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH43" t="n">
-        <v>2.93</v>
+        <v>1.38</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46092.69791666666</v>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O44" t="n">
         <v>3.48</v>
@@ -5696,7 +5696,7 @@
         <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z44" t="n">
         <v>2.88</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="O45" t="n">
-        <v>1.92</v>
+        <v>3.08</v>
       </c>
       <c r="P45" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.25</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
         <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="U45" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V45" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.85</v>
+        <v>5.2</v>
       </c>
       <c r="AA45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.55</v>
       </c>
-      <c r="AE45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH45" t="n">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46092.70833333334</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P47" t="n">
         <v>2.5</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q47" t="n">
-        <v>3.05</v>
+        <v>6.25</v>
       </c>
       <c r="R47" t="n">
         <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T47" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="U47" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V47" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.2</v>
+        <v>4.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.47</v>
+        <v>2.62</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46092.70833333334</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M49" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="N49" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="O49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46092.79166666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="N50" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46092.79166666666</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI53"/>
+  <dimension ref="A1:BI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,125 +488,255 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Goals_H_2T</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Goals_A_2T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cantos_H</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Cantos_A</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_FT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_FT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_FT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_HT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under25</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over45</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under45</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_A</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_75</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_85</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_95</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_105</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_115</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_75</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_85</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_95</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_105</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_115</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_2</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_over05</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_over15</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under05</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under15</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under25</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -653,81 +783,159 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>3.5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>3.5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="R2" t="n">
         <v>1.85</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
         <v>3.9</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="U2" t="n">
         <v>2.38</v>
       </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
         <v>1.25</v>
       </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
         <v>3.17</v>
       </c>
-      <c r="T2" t="n">
+      <c r="X2" t="n">
         <v>2.25</v>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>1.52</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
         <v>5.2</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AA2" t="n">
         <v>1.1</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AC2" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AD2" t="n">
         <v>4.45</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AE2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AF2" t="n">
         <v>2.32</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AG2" t="n">
         <v>2.35</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AH2" t="n">
         <v>1.52</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AI2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.52</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AL2" t="n">
         <v>2.34</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AM2" t="n">
         <v>1.21</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AN2" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="3" t="n">
         <v>46092.3125</v>
       </c>
     </row>
@@ -772,81 +980,159 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>6.8</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>1.15</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>9.6</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
         <v>2.84</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="U3" t="n">
         <v>1.5</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
         <v>1.21</v>
       </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
         <v>3.58</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
         <v>2.11</v>
       </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
         <v>1.66</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
         <v>4.25</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
         <v>1.15</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AC3" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AD3" t="n">
         <v>5.2</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
         <v>1.42</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
         <v>2.72</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
         <v>2.18</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
         <v>1.68</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK3" t="n">
         <v>2.03</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AL3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AM3" t="n">
         <v>1.05</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AN3" t="n">
         <v>1.04</v>
       </c>
-      <c r="AI3" s="3" t="n">
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="3" t="n">
         <v>46092.3125</v>
       </c>
     </row>
@@ -891,81 +1177,159 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>2.96</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>2.19</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>3.5</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="U4" t="n">
         <v>2.79</v>
       </c>
-      <c r="R4" t="n">
+      <c r="V4" t="n">
         <v>1.47</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
         <v>2.41</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
         <v>3.32</v>
       </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
         <v>1.26</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Z4" t="n">
         <v>8.9</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
         <v>1.05</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AD4" t="n">
         <v>2.59</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
         <v>1.56</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
         <v>3.6</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AH4" t="n">
         <v>1.14</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AI4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.98</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AL4" t="n">
         <v>1.72</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AM4" t="n">
         <v>1.61</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AN4" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI4" s="3" t="n">
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="3" t="n">
         <v>46092.33333333334</v>
       </c>
     </row>
@@ -1010,23 +1374,23 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -1084,7 +1448,85 @@
       <c r="AH5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" s="3" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="3" t="n">
         <v>46092.35416666666</v>
       </c>
     </row>
@@ -1129,23 +1571,23 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
@@ -1203,7 +1645,85 @@
       <c r="AH6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" s="3" t="n">
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="3" t="n">
         <v>46092.375</v>
       </c>
     </row>
@@ -1248,23 +1768,23 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -1322,7 +1842,85 @@
       <c r="AH7" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" s="3" t="n">
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="3" t="n">
         <v>46092.41666666666</v>
       </c>
     </row>
@@ -1367,81 +1965,159 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>4.33</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>3.4</v>
       </c>
-      <c r="N8" t="n">
+      <c r="R8" t="n">
         <v>1.7</v>
       </c>
-      <c r="O8" t="n">
+      <c r="S8" t="n">
         <v>5.43</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="U8" t="n">
         <v>2.26</v>
       </c>
-      <c r="R8" t="n">
+      <c r="V8" t="n">
         <v>1.38</v>
       </c>
-      <c r="S8" t="n">
+      <c r="W8" t="n">
         <v>2.7</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>2.8</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
         <v>1.33</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
         <v>7.8</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
         <v>1.02</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AB8" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AC8" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AD8" t="n">
         <v>3.18</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
         <v>1.99</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AF8" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AG8" t="n">
         <v>3.56</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AH8" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AI8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.78</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AL8" t="n">
         <v>1.77</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AM8" t="n">
         <v>2</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AN8" t="n">
         <v>1.12</v>
       </c>
-      <c r="AI8" s="3" t="n">
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="3" t="n">
         <v>46092.41666666666</v>
       </c>
     </row>
@@ -1486,23 +2162,23 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1560,7 +2236,85 @@
       <c r="AH9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" s="3" t="n">
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="3" t="n">
         <v>46092.4375</v>
       </c>
     </row>
@@ -1605,23 +2359,23 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1679,7 +2433,85 @@
       <c r="AH10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" s="3" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3" t="n">
         <v>46092.4375</v>
       </c>
     </row>
@@ -1724,81 +2556,159 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.84</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI11" s="3" t="n">
+      <c r="AI11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="3" t="n">
         <v>46092.4375</v>
       </c>
     </row>
@@ -1843,23 +2753,23 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1917,7 +2827,85 @@
       <c r="AH12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="3" t="n">
         <v>46092.45833333334</v>
       </c>
     </row>
@@ -1962,23 +2950,23 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
@@ -2036,7 +3024,85 @@
       <c r="AH13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" s="3" t="n">
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="3" t="n">
         <v>46092.47916666666</v>
       </c>
     </row>
@@ -2081,23 +3147,23 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
@@ -2155,7 +3221,85 @@
       <c r="AH14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="n">
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="3" t="n">
         <v>46092.47916666666</v>
       </c>
     </row>
@@ -2200,23 +3344,23 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
@@ -2274,7 +3418,85 @@
       <c r="AH15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" s="3" t="n">
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
         <v>46092.48958333334</v>
       </c>
     </row>
@@ -2319,23 +3541,23 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -2393,7 +3615,85 @@
       <c r="AH16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="3" t="n">
         <v>46092.52083333334</v>
       </c>
     </row>
@@ -2438,31 +3738,31 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
+      <c r="K17" t="n">
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2489,30 +3789,108 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AF17" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="3" t="n">
         <v>46092.52083333334</v>
       </c>
     </row>
@@ -2557,81 +3935,159 @@
       <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="P18" t="n">
         <v>2.1</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
         <v>3.76</v>
       </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
         <v>2.9</v>
       </c>
-      <c r="O18" t="n">
+      <c r="S18" t="n">
         <v>2.54</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.34</v>
       </c>
       <c r="T18" t="n">
         <v>2.31</v>
       </c>
       <c r="U18" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.54</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Z18" t="n">
         <v>5</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
         <v>1.1</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AC18" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AD18" t="n">
         <v>4.33</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AE18" t="n">
         <v>1.59</v>
       </c>
-      <c r="AB18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AF18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.43</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AH18" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AI18" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AL18" t="n">
         <v>2.36</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AM18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AN18" t="n">
         <v>1.63</v>
       </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="3" t="n">
         <v>46092.54166666666</v>
       </c>
     </row>
@@ -2676,41 +4132,41 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="P19" t="n">
         <v>1.98</v>
       </c>
-      <c r="M19" t="n">
+      <c r="Q19" t="n">
         <v>3.2</v>
       </c>
-      <c r="N19" t="n">
+      <c r="R19" t="n">
         <v>3.4</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>2.75</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>3.75</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
@@ -2727,30 +4183,108 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="3" t="n">
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BI19" s="3" t="n">
         <v>46092.54166666666</v>
       </c>
     </row>
@@ -2795,81 +4329,159 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>1.66</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
         <v>4</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>3.7</v>
       </c>
-      <c r="O20" t="n">
+      <c r="S20" t="n">
         <v>2.15</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="U20" t="n">
         <v>4.24</v>
       </c>
-      <c r="R20" t="n">
+      <c r="V20" t="n">
         <v>1.25</v>
       </c>
-      <c r="S20" t="n">
+      <c r="W20" t="n">
         <v>3.82</v>
       </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
         <v>2.18</v>
       </c>
-      <c r="U20" t="n">
+      <c r="Y20" t="n">
         <v>1.6</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Z20" t="n">
         <v>4.8</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AA20" t="n">
         <v>1.11</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AB20" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AC20" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AD20" t="n">
         <v>5.1</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AE20" t="n">
         <v>1.56</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AF20" t="n">
         <v>2.48</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AG20" t="n">
         <v>2.32</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AI20" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.49</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AL20" t="n">
         <v>2.42</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AM20" t="n">
         <v>1.15</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AN20" t="n">
         <v>2.02</v>
       </c>
-      <c r="AI20" s="3" t="n">
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="3" t="n">
         <v>46092.58333333334</v>
       </c>
     </row>
@@ -2914,23 +4526,23 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
@@ -2988,7 +4600,85 @@
       <c r="AH21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" s="3" t="n">
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="3" t="n">
         <v>46092.60416666666</v>
       </c>
     </row>
@@ -3033,23 +4723,23 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +4797,85 @@
       <c r="AH22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="n">
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="3" t="n">
         <v>46092.60416666666</v>
       </c>
     </row>
@@ -3152,23 +4920,23 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
@@ -3226,7 +4994,85 @@
       <c r="AH23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" s="3" t="n">
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
         <v>46092.60416666666</v>
       </c>
     </row>
@@ -3271,23 +5117,23 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
@@ -3345,7 +5191,85 @@
       <c r="AH24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" s="3" t="n">
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
         <v>46092.60416666666</v>
       </c>
     </row>
@@ -3390,81 +5314,159 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="P25" t="n">
         <v>1.38</v>
       </c>
-      <c r="M25" t="n">
+      <c r="Q25" t="n">
         <v>4.1</v>
       </c>
-      <c r="N25" t="n">
+      <c r="R25" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="O25" t="n">
+      <c r="S25" t="n">
         <v>1.96</v>
       </c>
-      <c r="P25" t="n">
+      <c r="T25" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="R25" t="n">
+      <c r="V25" t="n">
         <v>1.44</v>
       </c>
-      <c r="S25" t="n">
+      <c r="W25" t="n">
         <v>2.5</v>
       </c>
-      <c r="T25" t="n">
+      <c r="X25" t="n">
         <v>3.18</v>
       </c>
-      <c r="U25" t="n">
+      <c r="Y25" t="n">
         <v>1.33</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Z25" t="n">
         <v>8.5</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AA25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AB25" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AC25" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AD25" t="n">
         <v>2.55</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AE25" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AG25" t="n">
         <v>4.2</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AH25" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AI25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK25" t="n">
         <v>3.06</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AL25" t="n">
         <v>1.29</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AM25" t="n">
         <v>1</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AN25" t="n">
         <v>2.8</v>
       </c>
-      <c r="AI25" s="3" t="n">
+      <c r="AO25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI25" s="3" t="n">
         <v>46092.60416666666</v>
       </c>
     </row>
@@ -3509,81 +5511,159 @@
       <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S26" t="n">
         <v>5.5</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.34</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.5</v>
       </c>
-      <c r="U26" t="n">
+      <c r="Y26" t="n">
         <v>1.48</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Z26" t="n">
         <v>6.35</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AA26" t="n">
         <v>1.09</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AB26" t="n">
         <v>1</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AC26" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
         <v>3.72</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AE26" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AF26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>3.15</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI26" s="3" t="n">
+      <c r="BA26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
         <v>46092.61458333334</v>
       </c>
     </row>
@@ -3628,23 +5708,23 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
@@ -3702,7 +5782,85 @@
       <c r="AH27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" s="3" t="n">
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3" t="n">
         <v>46092.61458333334</v>
       </c>
     </row>
@@ -3747,23 +5905,23 @@
       <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
@@ -3821,7 +5979,85 @@
       <c r="AH28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" s="3" t="n">
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3" t="n">
         <v>46092.625</v>
       </c>
     </row>
@@ -3866,23 +6102,23 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -3940,7 +6176,85 @@
       <c r="AH29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" s="3" t="n">
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3" t="n">
         <v>46092.625</v>
       </c>
     </row>
@@ -3985,23 +6299,23 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
@@ -4059,7 +6373,85 @@
       <c r="AH30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" s="3" t="n">
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="3" t="n">
         <v>46092.625</v>
       </c>
     </row>
@@ -4104,23 +6496,23 @@
       <c r="J31" t="n">
         <v>0</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -4178,7 +6570,85 @@
       <c r="AH31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" s="3" t="n">
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3" t="n">
         <v>46092.625</v>
       </c>
     </row>
@@ -4223,23 +6693,23 @@
       <c r="J32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
@@ -4297,7 +6767,85 @@
       <c r="AH32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="n">
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3" t="n">
         <v>46092.625</v>
       </c>
     </row>
@@ -4342,81 +6890,159 @@
       <c r="J33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.3</v>
       </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
         <v>2.7</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.34</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y33" t="n">
         <v>1.42</v>
       </c>
-      <c r="V33" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AC33" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AD33" t="n">
         <v>3.42</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AE33" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR33" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI33" s="3" t="n">
+      <c r="AS33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" s="3" t="n">
         <v>46092.66666666666</v>
       </c>
     </row>
@@ -4461,81 +7087,159 @@
       <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.77</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.87</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>1.24</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="BA34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB34" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AI34" s="3" t="n">
+      <c r="BC34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" s="3" t="n">
         <v>46092.66666666666</v>
       </c>
     </row>
@@ -4580,81 +7284,159 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="P35" t="n">
         <v>3.1</v>
       </c>
-      <c r="M35" t="n">
+      <c r="Q35" t="n">
         <v>3.7</v>
       </c>
-      <c r="N35" t="n">
-        <v>2</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="R35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.6</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="T35" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U35" t="n">
         <v>2.5</v>
       </c>
-      <c r="R35" t="n">
+      <c r="V35" t="n">
         <v>1.3</v>
       </c>
-      <c r="S35" t="n">
+      <c r="W35" t="n">
         <v>3.25</v>
       </c>
-      <c r="T35" t="n">
+      <c r="X35" t="n">
         <v>2.4</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z35" t="n">
         <v>5.75</v>
       </c>
-      <c r="W35" t="n">
+      <c r="AA35" t="n">
         <v>1.07</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AB35" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AC35" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AD35" t="n">
         <v>4.1</v>
       </c>
-      <c r="AA35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.56</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AL35" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AM35" t="n">
         <v>1.21</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AN35" t="n">
         <v>1.26</v>
       </c>
-      <c r="AI35" s="3" t="n">
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" s="3" t="n">
         <v>46092.66666666666</v>
       </c>
     </row>
@@ -4699,81 +7481,159 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="P36" t="n">
         <v>4.25</v>
       </c>
-      <c r="M36" t="n">
+      <c r="Q36" t="n">
         <v>3.2</v>
       </c>
-      <c r="N36" t="n">
+      <c r="R36" t="n">
         <v>1.85</v>
       </c>
-      <c r="O36" t="n">
+      <c r="S36" t="n">
         <v>5.34</v>
       </c>
-      <c r="P36" t="n">
+      <c r="T36" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="U36" t="n">
         <v>2.54</v>
       </c>
-      <c r="R36" t="n">
+      <c r="V36" t="n">
         <v>1.52</v>
       </c>
-      <c r="S36" t="n">
+      <c r="W36" t="n">
         <v>2.44</v>
       </c>
-      <c r="T36" t="n">
+      <c r="X36" t="n">
         <v>3.3</v>
       </c>
-      <c r="U36" t="n">
+      <c r="Y36" t="n">
         <v>1.25</v>
       </c>
-      <c r="V36" t="n">
+      <c r="Z36" t="n">
         <v>10</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AA36" t="n">
         <v>1.01</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AB36" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AC36" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AD36" t="n">
         <v>2.43</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AE36" t="n">
         <v>2.35</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AF36" t="n">
         <v>1.45</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AG36" t="n">
         <v>4.8</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AH36" t="n">
         <v>1.13</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AI36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK36" t="n">
         <v>2.23</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AL36" t="n">
         <v>1.63</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AM36" t="n">
         <v>1.28</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AN36" t="n">
         <v>1.15</v>
       </c>
-      <c r="AI36" s="3" t="n">
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
         <v>46092.6875</v>
       </c>
     </row>
@@ -4818,81 +7678,159 @@
       <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>3.35</v>
       </c>
-      <c r="P37" t="n">
+      <c r="T37" t="n">
         <v>1.69</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="U37" t="n">
         <v>4.28</v>
       </c>
-      <c r="R37" t="n">
+      <c r="V37" t="n">
         <v>1.72</v>
       </c>
-      <c r="S37" t="n">
+      <c r="W37" t="n">
         <v>1.99</v>
       </c>
-      <c r="T37" t="n">
+      <c r="X37" t="n">
         <v>3.94</v>
       </c>
-      <c r="U37" t="n">
+      <c r="Y37" t="n">
         <v>1.17</v>
       </c>
-      <c r="V37" t="n">
+      <c r="Z37" t="n">
         <v>13</v>
       </c>
-      <c r="W37" t="n">
+      <c r="AA37" t="n">
         <v>1.01</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AB37" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AC37" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AD37" t="n">
         <v>2.14</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AE37" t="n">
         <v>2.83</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AF37" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AG37" t="n">
         <v>6.34</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AH37" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AI37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AL37" t="n">
         <v>1.56</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AM37" t="n">
         <v>1.38</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AN37" t="n">
         <v>1.38</v>
       </c>
-      <c r="AI37" s="3" t="n">
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" s="3" t="n">
         <v>46092.6875</v>
       </c>
     </row>
@@ -4937,81 +7875,159 @@
       <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="P38" t="n">
         <v>1.75</v>
       </c>
-      <c r="M38" t="n">
+      <c r="Q38" t="n">
         <v>3.7</v>
       </c>
-      <c r="N38" t="n">
+      <c r="R38" t="n">
         <v>4.5</v>
       </c>
-      <c r="O38" t="n">
+      <c r="S38" t="n">
         <v>2.3</v>
       </c>
-      <c r="P38" t="n">
+      <c r="T38" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="U38" t="n">
         <v>5.25</v>
       </c>
-      <c r="R38" t="n">
+      <c r="V38" t="n">
         <v>1.38</v>
       </c>
-      <c r="S38" t="n">
+      <c r="W38" t="n">
         <v>2.95</v>
       </c>
-      <c r="T38" t="n">
+      <c r="X38" t="n">
         <v>2.7</v>
       </c>
-      <c r="U38" t="n">
+      <c r="Y38" t="n">
         <v>1.36</v>
       </c>
-      <c r="V38" t="n">
+      <c r="Z38" t="n">
         <v>7.4</v>
       </c>
-      <c r="W38" t="n">
+      <c r="AA38" t="n">
         <v>1.07</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AB38" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AC38" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AD38" t="n">
         <v>3.24</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AE38" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AF38" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AG38" t="n">
         <v>3.3</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AH38" t="n">
         <v>1.31</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AI38" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.9</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AL38" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AM38" t="n">
         <v>1.16</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AN38" t="n">
         <v>1.95</v>
       </c>
-      <c r="AI38" s="3" t="n">
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5056,81 +8072,159 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="P39" t="n">
         <v>2.94</v>
       </c>
-      <c r="M39" t="n">
+      <c r="Q39" t="n">
         <v>3.28</v>
       </c>
-      <c r="N39" t="n">
+      <c r="R39" t="n">
         <v>2.37</v>
       </c>
-      <c r="O39" t="n">
+      <c r="S39" t="n">
         <v>3.72</v>
       </c>
-      <c r="P39" t="n">
+      <c r="T39" t="n">
         <v>2.03</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="U39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" t="n">
+      <c r="V39" t="n">
         <v>1.43</v>
       </c>
-      <c r="S39" t="n">
+      <c r="W39" t="n">
         <v>2.62</v>
       </c>
-      <c r="T39" t="n">
+      <c r="X39" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V39" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
         <v>1.32</v>
       </c>
       <c r="Z39" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.88</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AE39" t="n">
         <v>2.13</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AF39" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AG39" t="n">
         <v>4.45</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AH39" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AI39" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AL39" t="n">
         <v>1.87</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AM39" t="n">
         <v>1.31</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AN39" t="n">
         <v>1.37</v>
       </c>
-      <c r="AI39" s="3" t="n">
+      <c r="AO39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BI39" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5175,81 +8269,159 @@
       <c r="J40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="P40" t="n">
         <v>2.45</v>
       </c>
-      <c r="M40" t="n">
+      <c r="Q40" t="n">
         <v>3.5</v>
       </c>
-      <c r="N40" t="n">
+      <c r="R40" t="n">
         <v>2.7</v>
       </c>
-      <c r="O40" t="n">
+      <c r="S40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
+      <c r="T40" t="n">
         <v>2.19</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="U40" t="n">
         <v>3</v>
       </c>
-      <c r="R40" t="n">
+      <c r="V40" t="n">
         <v>1.32</v>
       </c>
-      <c r="S40" t="n">
+      <c r="W40" t="n">
         <v>3.1</v>
       </c>
-      <c r="T40" t="n">
+      <c r="X40" t="n">
         <v>2.61</v>
       </c>
-      <c r="U40" t="n">
+      <c r="Y40" t="n">
         <v>1.45</v>
       </c>
-      <c r="V40" t="n">
+      <c r="Z40" t="n">
         <v>5.5</v>
       </c>
-      <c r="W40" t="n">
+      <c r="AA40" t="n">
         <v>1.07</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AB40" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AC40" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AD40" t="n">
         <v>4.35</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AE40" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AF40" t="n">
         <v>2.08</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AG40" t="n">
         <v>2.76</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AH40" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AI40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK40" t="n">
         <v>1.6</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AL40" t="n">
         <v>2.33</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AM40" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AN40" t="n">
         <v>1.49</v>
       </c>
-      <c r="AI40" s="3" t="n">
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5294,81 +8466,159 @@
       <c r="J41" t="n">
         <v>0</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="P41" t="n">
         <v>2.68</v>
       </c>
-      <c r="M41" t="n">
+      <c r="Q41" t="n">
         <v>3.4</v>
       </c>
-      <c r="N41" t="n">
+      <c r="R41" t="n">
         <v>2.55</v>
       </c>
-      <c r="O41" t="n">
+      <c r="S41" t="n">
         <v>3.04</v>
       </c>
-      <c r="P41" t="n">
+      <c r="T41" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="U41" t="n">
         <v>3.1</v>
       </c>
-      <c r="R41" t="n">
+      <c r="V41" t="n">
         <v>1.39</v>
       </c>
-      <c r="S41" t="n">
+      <c r="W41" t="n">
         <v>2.77</v>
       </c>
-      <c r="T41" t="n">
+      <c r="X41" t="n">
         <v>2.6</v>
       </c>
-      <c r="U41" t="n">
+      <c r="Y41" t="n">
         <v>1.39</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Z41" t="n">
         <v>6.25</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AA41" t="n">
         <v>1.05</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AB41" t="n">
         <v>1</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AC41" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AD41" t="n">
         <v>3.38</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AE41" t="n">
         <v>1.79</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AF41" t="n">
         <v>1.88</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AG41" t="n">
         <v>3.05</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AH41" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AI41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AL41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AM41" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AN41" t="n">
         <v>1.43</v>
       </c>
-      <c r="AI41" s="3" t="n">
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5413,81 +8663,159 @@
       <c r="J42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="P42" t="n">
         <v>2.7</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.04</v>
       </c>
       <c r="Q42" t="n">
         <v>3.2</v>
       </c>
       <c r="R42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V42" t="n">
         <v>1.48</v>
       </c>
-      <c r="S42" t="n">
+      <c r="W42" t="n">
         <v>2.65</v>
       </c>
-      <c r="T42" t="n">
+      <c r="X42" t="n">
         <v>3.1</v>
       </c>
-      <c r="U42" t="n">
+      <c r="Y42" t="n">
         <v>1.33</v>
       </c>
-      <c r="V42" t="n">
+      <c r="Z42" t="n">
         <v>8.5</v>
       </c>
-      <c r="W42" t="n">
+      <c r="AA42" t="n">
         <v>1.03</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AB42" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AC42" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AD42" t="n">
         <v>2.88</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AE42" t="n">
         <v>2.18</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AF42" t="n">
         <v>1.66</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AG42" t="n">
         <v>3.7</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AH42" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AI42" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AL42" t="n">
         <v>1.84</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AM42" t="n">
         <v>1.35</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AN42" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI42" s="3" t="n">
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5532,81 +8860,159 @@
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="P43" t="n">
         <v>1.46</v>
       </c>
-      <c r="M43" t="n">
+      <c r="Q43" t="n">
         <v>4.6</v>
       </c>
-      <c r="N43" t="n">
+      <c r="R43" t="n">
         <v>6.5</v>
       </c>
-      <c r="O43" t="n">
+      <c r="S43" t="n">
         <v>1.85</v>
       </c>
-      <c r="P43" t="n">
+      <c r="T43" t="n">
         <v>2.43</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="U43" t="n">
         <v>6.1</v>
       </c>
-      <c r="R43" t="n">
+      <c r="V43" t="n">
         <v>1.3</v>
       </c>
-      <c r="S43" t="n">
+      <c r="W43" t="n">
         <v>3.02</v>
       </c>
-      <c r="T43" t="n">
+      <c r="X43" t="n">
         <v>2.65</v>
       </c>
-      <c r="U43" t="n">
+      <c r="Y43" t="n">
         <v>1.42</v>
       </c>
-      <c r="V43" t="n">
+      <c r="Z43" t="n">
         <v>6</v>
       </c>
-      <c r="W43" t="n">
+      <c r="AA43" t="n">
         <v>1.06</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AB43" t="n">
         <v>1</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AC43" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AD43" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AE43" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AF43" t="n">
         <v>2</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AG43" t="n">
         <v>3</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AH43" t="n">
         <v>1.32</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AI43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK43" t="n">
         <v>2.12</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AL43" t="n">
         <v>1.69</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AM43" t="n">
         <v>1.17</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AN43" t="n">
         <v>2.93</v>
       </c>
-      <c r="AI43" s="3" t="n">
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5651,81 +9057,159 @@
       <c r="J44" t="n">
         <v>0</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="P44" t="n">
         <v>2.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="Q44" t="n">
         <v>3.4</v>
       </c>
-      <c r="N44" t="n">
+      <c r="R44" t="n">
         <v>3.25</v>
       </c>
-      <c r="O44" t="n">
+      <c r="S44" t="n">
         <v>2.62</v>
       </c>
-      <c r="P44" t="n">
+      <c r="T44" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="U44" t="n">
         <v>3.6</v>
       </c>
-      <c r="R44" t="n">
+      <c r="V44" t="n">
         <v>1.38</v>
       </c>
-      <c r="S44" t="n">
+      <c r="W44" t="n">
         <v>2.73</v>
       </c>
-      <c r="T44" t="n">
+      <c r="X44" t="n">
         <v>2.75</v>
       </c>
-      <c r="U44" t="n">
+      <c r="Y44" t="n">
         <v>1.37</v>
       </c>
-      <c r="V44" t="n">
+      <c r="Z44" t="n">
         <v>7.5</v>
       </c>
-      <c r="W44" t="n">
+      <c r="AA44" t="n">
         <v>1.04</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AB44" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AC44" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AD44" t="n">
         <v>3.4</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AE44" t="n">
         <v>1.87</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AF44" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AG44" t="n">
         <v>3.46</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AH44" t="n">
         <v>1.26</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AI44" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.67</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AL44" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AM44" t="n">
         <v>1.24</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AN44" t="n">
         <v>1.65</v>
       </c>
-      <c r="AI44" s="3" t="n">
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
         <v>46092.69791666666</v>
       </c>
     </row>
@@ -5770,81 +9254,159 @@
       <c r="J45" t="n">
         <v>0</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M45" t="n">
+      <c r="P45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W45" t="n">
         <v>3.5</v>
       </c>
-      <c r="N45" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T45" t="n">
+      <c r="X45" t="n">
         <v>2.35</v>
       </c>
-      <c r="U45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V45" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y45" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="Z45" t="n">
         <v>5.2</v>
       </c>
       <c r="AA45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB45" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC45" t="n">
+      <c r="AF45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG45" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AH45" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AI45" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK45" t="n">
         <v>1.48</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AL45" t="n">
         <v>2.6</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AM45" t="n">
         <v>1.55</v>
       </c>
-      <c r="AH45" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI45" s="3" t="n">
+      <c r="AN45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="3" t="n">
         <v>46092.70833333334</v>
       </c>
     </row>
@@ -5889,81 +9451,159 @@
       <c r="J46" t="n">
         <v>0</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U46" t="n">
         <v>4.05</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="V46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BF46" t="n">
         <v>1.28</v>
       </c>
-      <c r="S46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V46" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AI46" s="3" t="n">
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
         <v>46092.70833333334</v>
       </c>
     </row>
@@ -6008,81 +9648,159 @@
       <c r="J47" t="n">
         <v>0</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R47" t="n">
         <v>2</v>
       </c>
-      <c r="O47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="S47" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T47" t="n">
         <v>2.43</v>
       </c>
-      <c r="Q47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V47" t="n">
         <v>1.28</v>
       </c>
-      <c r="S47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V47" t="n">
-        <v>5.05</v>
-      </c>
       <c r="W47" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA47" t="n">
         <v>1.15</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AB47" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AC47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z47" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE47" t="n">
+      <c r="AK47" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF47" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AG47" t="n">
+      <c r="AL47" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN47" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI47" s="3" t="n">
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="3" t="n">
         <v>46092.70833333334</v>
       </c>
     </row>
@@ -6127,81 +9845,159 @@
       <c r="J48" t="n">
         <v>0</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="P48" t="n">
         <v>1.44</v>
       </c>
-      <c r="M48" t="n">
+      <c r="Q48" t="n">
         <v>4.6</v>
       </c>
-      <c r="N48" t="n">
+      <c r="R48" t="n">
         <v>6</v>
       </c>
-      <c r="O48" t="n">
+      <c r="S48" t="n">
         <v>1.92</v>
       </c>
-      <c r="P48" t="n">
+      <c r="T48" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="U48" t="n">
         <v>6.25</v>
       </c>
-      <c r="R48" t="n">
+      <c r="V48" t="n">
         <v>1.25</v>
       </c>
-      <c r="S48" t="n">
+      <c r="W48" t="n">
         <v>3.42</v>
       </c>
-      <c r="T48" t="n">
+      <c r="X48" t="n">
         <v>2.29</v>
       </c>
-      <c r="U48" t="n">
+      <c r="Y48" t="n">
         <v>1.58</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Z48" t="n">
         <v>4.75</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AA48" t="n">
         <v>1.12</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AB48" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AC48" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AD48" t="n">
         <v>4.85</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AE48" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AF48" t="n">
         <v>2.5</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AG48" t="n">
         <v>2.4</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AH48" t="n">
         <v>1.55</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AI48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.66</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AL48" t="n">
         <v>2</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AM48" t="n">
         <v>1.17</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AN48" t="n">
         <v>2.62</v>
       </c>
-      <c r="AI48" s="3" t="n">
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="3" t="n">
         <v>46092.70833333334</v>
       </c>
     </row>
@@ -6246,81 +10042,159 @@
       <c r="J49" t="n">
         <v>0</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S49" t="n">
         <v>2.45</v>
       </c>
-      <c r="P49" t="n">
+      <c r="T49" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="U49" t="n">
         <v>4</v>
       </c>
-      <c r="R49" t="n">
+      <c r="V49" t="n">
         <v>1.38</v>
       </c>
-      <c r="S49" t="n">
+      <c r="W49" t="n">
         <v>2.81</v>
       </c>
-      <c r="T49" t="n">
+      <c r="X49" t="n">
         <v>2.73</v>
       </c>
-      <c r="U49" t="n">
+      <c r="Y49" t="n">
         <v>1.4</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Z49" t="n">
         <v>7</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AA49" t="n">
         <v>1.06</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AB49" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AC49" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AD49" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG49" t="n">
         <v>3.4</v>
       </c>
-      <c r="AA49" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI49" s="3" t="n">
+      <c r="BA49" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI49" s="3" t="n">
         <v>46092.79166666666</v>
       </c>
     </row>
@@ -6365,32 +10239,32 @@
       <c r="J50" t="n">
         <v>0</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="P50" t="n">
         <v>2.5</v>
       </c>
-      <c r="M50" t="n">
+      <c r="Q50" t="n">
         <v>3.38</v>
       </c>
-      <c r="N50" t="n">
+      <c r="R50" t="n">
         <v>2.89</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
@@ -6416,30 +10290,108 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
         <v>2</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AF50" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
       <c r="AG50" t="n">
         <v>0</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" s="3" t="n">
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI50" s="3" t="n">
         <v>46092.79166666666</v>
       </c>
     </row>
@@ -6484,81 +10436,159 @@
       <c r="J51" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="P51" t="n">
         <v>1.74</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="S51" t="n">
         <v>2.25</v>
       </c>
-      <c r="P51" t="n">
+      <c r="T51" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="U51" t="n">
         <v>4.5</v>
       </c>
-      <c r="R51" t="n">
+      <c r="V51" t="n">
         <v>1.38</v>
       </c>
-      <c r="S51" t="n">
+      <c r="W51" t="n">
         <v>2.81</v>
       </c>
-      <c r="T51" t="n">
+      <c r="X51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG51" t="n">
         <v>2.85</v>
       </c>
-      <c r="U51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD51" t="n">
+      <c r="AH51" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AI51" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AL51" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AM51" t="n">
         <v>1.2</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AN51" t="n">
         <v>2.05</v>
       </c>
-      <c r="AI51" s="3" t="n">
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="3" t="n">
         <v>46092.83333333334</v>
       </c>
     </row>
@@ -6603,81 +10633,159 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R52" t="n">
         <v>6</v>
       </c>
-      <c r="O52" t="n">
+      <c r="S52" t="n">
         <v>2.19</v>
       </c>
-      <c r="P52" t="n">
+      <c r="T52" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="U52" t="n">
         <v>6</v>
       </c>
-      <c r="R52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S52" t="n">
+      <c r="V52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W52" t="n">
         <v>2.73</v>
       </c>
-      <c r="T52" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="X52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC52" t="n">
         <v>1.34</v>
       </c>
-      <c r="V52" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA52" t="n">
+      <c r="AD52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE52" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB52" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC52" t="n">
+      <c r="AF52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG52" t="n">
         <v>3.82</v>
       </c>
-      <c r="AD52" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE52" t="n">
+      <c r="AH52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK52" t="n">
         <v>2.04</v>
       </c>
-      <c r="AF52" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI52" s="3" t="n">
+      <c r="AL52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="3" t="n">
         <v>46092.89583333334</v>
       </c>
     </row>
@@ -6722,81 +10830,159 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N53" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.02</v>
-      </c>
       <c r="P53" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="T53" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q53" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
+        <v>6</v>
+      </c>
+      <c r="V53" t="n">
         <v>1.36</v>
       </c>
-      <c r="S53" t="n">
+      <c r="W53" t="n">
         <v>2.89</v>
       </c>
-      <c r="T53" t="n">
+      <c r="X53" t="n">
         <v>2.6</v>
       </c>
-      <c r="U53" t="n">
+      <c r="Y53" t="n">
         <v>1.4</v>
       </c>
-      <c r="V53" t="n">
+      <c r="Z53" t="n">
         <v>6.5</v>
       </c>
-      <c r="W53" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X53" t="n">
+      <c r="AA53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB53" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="AC53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z53" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE53" t="n">
+      <c r="AI53" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK53" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG53" t="n">
+      <c r="AL53" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="BB53" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI53" s="3" t="n">
+      <c r="BC53" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="3" t="n">
         <v>46092.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -804,10 +804,10 @@
         <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S2" t="n">
         <v>3.9</v>
@@ -822,7 +822,7 @@
         <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="X2" t="n">
         <v>2.25</v>
@@ -1001,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>1.15</v>
@@ -1016,7 +1016,7 @@
         <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
         <v>3.58</v>
@@ -1040,7 +1040,7 @@
         <v>1.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="AE3" t="n">
         <v>1.42</v>
@@ -1049,7 +1049,7 @@
         <v>2.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="AH3" t="n">
         <v>1.68</v>
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
-        <v>5.43</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
         <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
         <v>2.7</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y8" t="n">
         <v>1.33</v>
@@ -2028,10 +2028,10 @@
         <v>3.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>3.56</v>
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="S20" t="n">
         <v>2.15</v>
@@ -4365,10 +4365,10 @@
         <v>4.24</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="X20" t="n">
         <v>2.18</v>
@@ -4380,7 +4380,7 @@
         <v>4.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AB20" t="n">
         <v>1.02</v>
@@ -4395,7 +4395,7 @@
         <v>1.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AG20" t="n">
         <v>2.32</v>
@@ -4410,7 +4410,7 @@
         <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AL20" t="n">
         <v>2.42</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5332,16 +5332,16 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="S25" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="T25" t="n">
         <v>2.15</v>
@@ -5353,64 +5353,64 @@
         <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X25" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AH25" t="n">
         <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.06</v>
+        <v>2.6</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AM25" t="n">
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="AO25" t="n">
         <v>1.17</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.85</v>
@@ -5431,7 +5431,7 @@
         <v>1.88</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AX25" t="n">
         <v>1.24</v>
@@ -5443,19 +5443,19 @@
         <v>1.28</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
         <v>1.36</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BF25" t="n">
         <v>1.07</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R34" t="n">
-        <v>7.6</v>
+        <v>1.96</v>
       </c>
       <c r="S34" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="U34" t="n">
-        <v>7.39</v>
+        <v>2.5</v>
       </c>
       <c r="V34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY34" t="n">
         <v>1.25</v>
       </c>
-      <c r="W34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>1.24</v>
+        <v>2.33</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.2</v>
+        <v>1.68</v>
       </c>
       <c r="BB34" t="n">
         <v>1.14</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.96</v>
+        <v>7.6</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="T35" t="n">
-        <v>2.21</v>
+        <v>2.69</v>
       </c>
       <c r="U35" t="n">
-        <v>2.5</v>
+        <v>7.39</v>
       </c>
       <c r="V35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
         <v>1.3</v>
       </c>
-      <c r="W35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM35" t="n">
+      <c r="AQ35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY35" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AZ35" t="n">
-        <v>2.33</v>
+        <v>1.24</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="BB35" t="n">
         <v>1.14</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7499,28 +7499,28 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S36" t="n">
         <v>5.34</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V36" t="n">
         <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="X36" t="n">
         <v>3.3</v>
@@ -7535,10 +7535,10 @@
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AD36" t="n">
         <v>2.43</v>
@@ -7553,7 +7553,7 @@
         <v>4.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI36" t="n">
         <v>8.800000000000001</v>
@@ -7562,10 +7562,10 @@
         <v>1.01</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AM36" t="n">
         <v>1.28</v>
@@ -7625,7 +7625,7 @@
         <v>1.43</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S37" t="n">
         <v>3.35</v>
@@ -7711,7 +7711,7 @@
         <v>1.69</v>
       </c>
       <c r="U37" t="n">
-        <v>4.28</v>
+        <v>4.05</v>
       </c>
       <c r="V37" t="n">
         <v>1.72</v>
@@ -7720,10 +7720,10 @@
         <v>1.99</v>
       </c>
       <c r="X37" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
         <v>13</v>
@@ -7735,19 +7735,19 @@
         <v>1.12</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AE37" t="n">
         <v>2.83</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>6.34</v>
+        <v>5.5</v>
       </c>
       <c r="AH37" t="n">
         <v>1.08</v>
@@ -7765,10 +7765,10 @@
         <v>1.56</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="X2" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="S3" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="X3" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.45</v>
+        <v>4.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.03</v>
+        <v>1.52</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,139 +5332,139 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7896,10 +7896,10 @@
         <v>1.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R38" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="S38" t="n">
         <v>2.3</v>
@@ -7908,16 +7908,16 @@
         <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="X38" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Y38" t="n">
         <v>1.36</v>
@@ -7926,13 +7926,13 @@
         <v>7.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB38" t="n">
         <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AD38" t="n">
         <v>3.24</v>
@@ -7944,10 +7944,10 @@
         <v>1.83</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI38" t="n">
         <v>6.55</v>
@@ -7956,7 +7956,7 @@
         <v>1.1</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL38" t="n">
         <v>1.85</v>
@@ -7965,19 +7965,19 @@
         <v>1.16</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AS38" t="n">
         <v>2.01</v>
@@ -7995,10 +7995,10 @@
         <v>2.13</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AZ38" t="n">
         <v>1.25</v>
@@ -8007,7 +8007,7 @@
         <v>5.59</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BC38" t="n">
         <v>2.2</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.94</v>
+        <v>1.34</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="R39" t="n">
-        <v>2.37</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S39" t="n">
-        <v>3.72</v>
+        <v>1.85</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="X39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV39" t="n">
         <v>2.75</v>
       </c>
-      <c r="Y39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR39" t="n">
+      <c r="AW39" t="n">
         <v>2.1</v>
       </c>
-      <c r="AS39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AX39" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.95</v>
+        <v>5.31</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -8287,19 +8287,19 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="U40" t="n">
         <v>3</v>
@@ -8308,16 +8308,16 @@
         <v>1.32</v>
       </c>
       <c r="W40" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X40" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="Y40" t="n">
         <v>1.45</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA40" t="n">
         <v>1.07</v>
@@ -8329,19 +8329,19 @@
         <v>1.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="AE40" t="n">
         <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AG40" t="n">
         <v>2.76</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AI40" t="n">
         <v>5.25</v>
@@ -8353,7 +8353,7 @@
         <v>1.6</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AM40" t="n">
         <v>1.27</v>
@@ -8377,22 +8377,22 @@
         <v>1.99</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.95</v>
+        <v>4.23</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AX40" t="n">
         <v>1.76</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AZ40" t="n">
         <v>1.95</v>
@@ -8413,7 +8413,7 @@
         <v>1.79</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q41" t="n">
         <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S41" t="n">
         <v>3.04</v>
@@ -8499,22 +8499,22 @@
         <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="V41" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="X41" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="AA41" t="n">
         <v>1.05</v>
@@ -8526,16 +8526,16 @@
         <v>1.24</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF41" t="n">
         <v>1.88</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="AH41" t="n">
         <v>1.29</v>
@@ -8547,7 +8547,7 @@
         <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL41" t="n">
         <v>2.1</v>
@@ -8556,7 +8556,7 @@
         <v>1.33</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8565,13 +8565,13 @@
         <v>1.21</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR41" t="n">
         <v>1.78</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AT41" t="n">
         <v>2.95</v>
@@ -8583,7 +8583,7 @@
         <v>2.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AX41" t="n">
         <v>1.57</v>
@@ -8592,25 +8592,25 @@
         <v>1.31</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BB41" t="n">
         <v>1.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8687,25 +8687,25 @@
         <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="S42" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="T42" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U42" t="n">
         <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
         <v>2.65</v>
       </c>
       <c r="X42" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="Y42" t="n">
         <v>1.33</v>
@@ -8714,100 +8714,100 @@
         <v>8.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AI42" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="BA42" t="n">
         <v>1.7</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="S43" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="T43" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="U43" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="V43" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W43" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="X43" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR43" t="n">
         <v>2</v>
       </c>
-      <c r="AG43" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK43" t="n">
+      <c r="AS43" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV43" t="n">
         <v>2.12</v>
       </c>
-      <c r="AL43" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR43" t="n">
+      <c r="AW43" t="n">
         <v>1.7</v>
       </c>
-      <c r="AS43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AX43" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.32</v>
+        <v>2.54</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,139 +9075,139 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="Q44" t="n">
         <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="S44" t="n">
-        <v>2.62</v>
+        <v>3.26</v>
       </c>
       <c r="T44" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="U44" t="n">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="V44" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W44" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="X44" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB44" t="n">
         <v>1.01</v>
       </c>
       <c r="AC44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM44" t="n">
         <v>1.31</v>
       </c>
-      <c r="AD44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE44" t="n">
+      <c r="AN44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW44" t="n">
         <v>1.87</v>
       </c>
-      <c r="AF44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL44" t="n">
+      <c r="AX44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA44" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ44" t="n">
+      <c r="BB44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE44" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR44" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF44" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BH44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BI44" s="3" t="n">
         <v>46092.69791666666</v>
@@ -9284,7 +9284,7 @@
         <v>3.08</v>
       </c>
       <c r="T45" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="U45" t="n">
         <v>3</v>
@@ -9299,7 +9299,7 @@
         <v>2.35</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z45" t="n">
         <v>5.2</v>
@@ -9314,13 +9314,13 @@
         <v>1.16</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AE45" t="n">
         <v>1.57</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG45" t="n">
         <v>2.38</v>
@@ -9472,13 +9472,13 @@
         <v>1.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="R46" t="n">
         <v>3.8</v>
       </c>
       <c r="S46" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="T46" t="n">
         <v>2.42</v>
@@ -9487,13 +9487,13 @@
         <v>4.05</v>
       </c>
       <c r="V46" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="X46" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="Y46" t="n">
         <v>1.55</v>
@@ -9502,31 +9502,31 @@
         <v>5.45</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
         <v>1.01</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AI46" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AJ46" t="n">
         <v>1.16</v>
@@ -9538,10 +9538,10 @@
         <v>2.5</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9559,28 +9559,28 @@
         <v>2.43</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AV46" t="n">
         <v>2.29</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BB46" t="n">
         <v>1.15</v>
@@ -9589,10 +9589,10 @@
         <v>1.8</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="BF46" t="n">
         <v>1.28</v>
@@ -9669,34 +9669,34 @@
         <v>3.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R47" t="n">
         <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="U47" t="n">
         <v>2.45</v>
       </c>
       <c r="V47" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W47" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="X47" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="AA47" t="n">
         <v>1.15</v>
@@ -9705,34 +9705,34 @@
         <v>1.02</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AE47" t="n">
         <v>1.61</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AI47" t="n">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK47" t="n">
         <v>1.5</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AM47" t="n">
         <v>1.28</v>
@@ -9753,13 +9753,13 @@
         <v>1.72</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="AV47" t="n">
         <v>2.6</v>
@@ -9771,7 +9771,7 @@
         <v>1.63</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AZ47" t="n">
         <v>2.25</v>
@@ -9783,13 +9783,13 @@
         <v>1.16</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="BE47" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="BF47" t="n">
         <v>1.28</v>
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
         <v>4.6</v>
       </c>
       <c r="R48" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="S48" t="n">
         <v>1.92</v>
@@ -9878,7 +9878,7 @@
         <v>2.5</v>
       </c>
       <c r="U48" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="V48" t="n">
         <v>1.25</v>
@@ -9896,7 +9896,7 @@
         <v>4.75</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB48" t="n">
         <v>1.04</v>
@@ -9911,7 +9911,7 @@
         <v>1.5</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AG48" t="n">
         <v>2.4</v>
@@ -9923,19 +9923,19 @@
         <v>3.9</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK48" t="n">
         <v>1.66</v>
       </c>
       <c r="AL48" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AM48" t="n">
         <v>1.17</v>
       </c>
       <c r="AN48" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9944,37 +9944,37 @@
         <v>1.19</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AR48" t="n">
         <v>1.7</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AU48" t="n">
         <v>3.84</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AY48" t="n">
         <v>1.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="BA48" t="n">
-        <v>8.1</v>
+        <v>3.9</v>
       </c>
       <c r="BB48" t="n">
         <v>1.13</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3953,34 +3953,34 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
         <v>2.9</v>
       </c>
       <c r="S18" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="X18" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Z18" t="n">
         <v>5</v>
@@ -4001,7 +4001,7 @@
         <v>1.59</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG18" t="n">
         <v>2.43</v>
@@ -4010,10 +4010,10 @@
         <v>1.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
         <v>1.53</v>
@@ -4022,10 +4022,10 @@
         <v>2.36</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4076,7 +4076,7 @@
         <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
         <v>1.22</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X33" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="Y33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF33" t="n">
         <v>2.25</v>
       </c>
-      <c r="U33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AG33" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX33" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AY33" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.76</v>
+        <v>4.45</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W34" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN34" t="n">
         <v>1.48</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.26</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,52 +7186,52 @@
         <v>1.26</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R35" t="n">
-        <v>7.6</v>
+        <v>1.96</v>
       </c>
       <c r="S35" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="U35" t="n">
-        <v>7.39</v>
+        <v>2.5</v>
       </c>
       <c r="V35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY35" t="n">
         <v>1.25</v>
       </c>
-      <c r="W35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AZ35" t="n">
-        <v>1.24</v>
+        <v>2.33</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.2</v>
+        <v>1.68</v>
       </c>
       <c r="BB35" t="n">
         <v>1.14</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,88 +7499,88 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
-        <v>5.34</v>
+        <v>3.35</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="U36" t="n">
-        <v>2.52</v>
+        <v>4.07</v>
       </c>
       <c r="V36" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="W36" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI36" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
         <v>2.38</v>
@@ -7592,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
         <v>1.5</v>
@@ -7607,25 +7607,25 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,88 +7696,88 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="S37" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="T37" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>4.05</v>
+        <v>2.52</v>
       </c>
       <c r="V37" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W37" t="n">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="X37" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA37" t="n">
         <v>1.01</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AI37" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR37" t="n">
         <v>2.38</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AW37" t="n">
         <v>1.5</v>
@@ -7804,25 +7804,25 @@
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.75</v>
+        <v>1.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="R38" t="n">
-        <v>4.75</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S38" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U38" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI38" t="n">
         <v>5.2</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>6.55</v>
       </c>
       <c r="AJ38" t="n">
         <v>1.1</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AM38" t="n">
         <v>1.16</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.07</v>
+        <v>2.98</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7974,28 +7974,28 @@
         <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.17</v>
+        <v>3.7</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AY38" t="n">
         <v>1.45</v>
@@ -8004,22 +8004,22 @@
         <v>1.25</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.59</v>
+        <v>5.31</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY39" t="n">
         <v>1.34</v>
       </c>
-      <c r="Q39" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U39" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ39" t="n">
+      <c r="AZ39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF39" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.51</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R40" t="n">
-        <v>2.6</v>
+        <v>4.75</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="X40" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.95</v>
+        <v>7.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.76</v>
+        <v>3.24</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AI40" t="n">
-        <v>5.25</v>
+        <v>6.55</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.49</v>
+        <v>2.07</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AU40" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.35</v>
+        <v>5.59</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,139 +8484,139 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q41" t="n">
         <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S41" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X41" t="n">
         <v>3.04</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.65</v>
-      </c>
       <c r="Y41" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.65</v>
+        <v>7.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AB41" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.23</v>
+        <v>4.43</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AL41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AS41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB41" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW41" t="n">
+      <c r="BC41" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG41" t="n">
         <v>1.95</v>
       </c>
-      <c r="AX41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0</v>
-      </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46092.69791666666</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="Q42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W42" t="n">
         <v>3.2</v>
       </c>
-      <c r="R42" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.65</v>
-      </c>
       <c r="X42" t="n">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ42" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z42" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN42" t="n">
+      <c r="AR42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY42" t="n">
         <v>1.43</v>
       </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
+      <c r="AZ42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BF42" t="n">
         <v>1.19</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q43" t="n">
         <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="S43" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="T43" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="V43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.4</v>
       </c>
-      <c r="W43" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z43" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="AE43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW43" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF43" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV43" t="n">
+      <c r="AX43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA43" t="n">
         <v>2.12</v>
       </c>
-      <c r="AW43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BB43" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,139 +9075,139 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
         <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="S44" t="n">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="U44" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="V44" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
         <v>2.65</v>
       </c>
       <c r="X44" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB44" t="n">
         <v>1.01</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG44" t="n">
-        <v>4.43</v>
+        <v>3.7</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AI44" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AO44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BH44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
         <v>46092.69791666666</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,130 +9272,130 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R45" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="S45" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="V45" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W45" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="X45" t="n">
         <v>2.35</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AB45" t="n">
         <v>1.01</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AG45" t="n">
         <v>2.38</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AL45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA45" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>1.88</v>
       </c>
       <c r="BB45" t="n">
         <v>1.15</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.85</v>
+        <v>5.05</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BF45" t="n">
         <v>1.28</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="R46" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="S46" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="T46" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U46" t="n">
-        <v>4.05</v>
+        <v>5.75</v>
       </c>
       <c r="V46" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
         <v>3.42</v>
       </c>
       <c r="X46" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z46" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AI46" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.94</v>
+        <v>2.64</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.95</v>
+        <v>3.84</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AY46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF46" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q48" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R48" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W48" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH48" t="n">
+      <c r="AI48" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM48" t="n">
         <v>1.55</v>
       </c>
-      <c r="AI48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AN48" t="n">
-        <v>2.64</v>
+        <v>1.46</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9944,52 +9944,52 @@
         <v>1.19</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="BA48" t="n">
-        <v>3.9</v>
+        <v>1.88</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R49" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="S49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AE50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL50" t="n">
         <v>2</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="S2" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.84</v>
+        <v>2.26</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="X2" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.45</v>
+        <v>4.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.03</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="X3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,143 +3949,143 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R18" t="n">
         <v>3.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.9</v>
-      </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH18" t="n">
         <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,83 +4146,83 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,25 +4264,25 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
         <v>46092.54166666666</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,88 +7499,88 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="S36" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>4.07</v>
+        <v>2.52</v>
       </c>
       <c r="V36" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="X36" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA36" t="n">
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AI36" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR36" t="n">
         <v>2.38</v>
@@ -7592,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AW36" t="n">
         <v>1.5</v>
@@ -7607,25 +7607,25 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,88 +7696,88 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R37" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="S37" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="U37" t="n">
-        <v>2.52</v>
+        <v>4.07</v>
       </c>
       <c r="V37" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="W37" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
         <v>1.01</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI37" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
         <v>2.38</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
         <v>1.5</v>
@@ -7804,25 +7804,25 @@
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.34</v>
       </c>
-      <c r="Q38" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R38" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U38" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB38" t="n">
         <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AF38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR38" t="n">
         <v>2</v>
       </c>
-      <c r="AG38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK38" t="n">
+      <c r="AS38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV38" t="n">
         <v>2.12</v>
       </c>
-      <c r="AL38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR38" t="n">
+      <c r="AW38" t="n">
         <v>1.7</v>
       </c>
-      <c r="AS38" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AX38" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.31</v>
+        <v>2.54</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="S39" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="T39" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="U39" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="V39" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W39" t="n">
         <v>2.65</v>
       </c>
       <c r="X39" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC39" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,139 +8484,139 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.81</v>
+        <v>1.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="R41" t="n">
-        <v>2.3</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S41" t="n">
-        <v>3.26</v>
+        <v>1.85</v>
       </c>
       <c r="T41" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>2.78</v>
+        <v>6.1</v>
       </c>
       <c r="V41" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W41" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="X41" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB41" t="n">
         <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.11</v>
+        <v>1.77</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.43</v>
+        <v>2.95</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI41" t="n">
-        <v>6.25</v>
+        <v>5.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.35</v>
+        <v>2.98</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AR41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AS41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AX41" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.95</v>
+        <v>5.31</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46092.69791666666</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U44" t="n">
         <v>3.2</v>
       </c>
-      <c r="S44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U44" t="n">
-        <v>3.7</v>
-      </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
         <v>2.65</v>
       </c>
       <c r="X44" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AH44" t="n">
         <v>1.23</v>
       </c>
       <c r="AI44" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AR44" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="AW44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BA44" t="n">
         <v>1.7</v>
       </c>
-      <c r="AX44" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BB44" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,43 +9666,43 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="S47" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="T47" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="U47" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W47" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="X47" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA47" t="n">
         <v>1.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC47" t="n">
         <v>1.16</v>
@@ -9711,79 +9711,79 @@
         <v>4.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX47" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI47" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AY47" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="BD47" t="n">
         <v>4.85</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,43 +9863,43 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R48" t="n">
+        <v>2</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.45</v>
       </c>
-      <c r="S48" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="V48" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W48" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="X48" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA48" t="n">
         <v>1.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC48" t="n">
         <v>1.16</v>
@@ -9908,79 +9908,79 @@
         <v>4.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG48" t="n">
         <v>2.35</v>
       </c>
-      <c r="AG48" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AH48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI48" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AL48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV48" t="n">
         <v>2.6</v>
       </c>
-      <c r="AM48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.64</v>
-      </c>
       <c r="AW48" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BD48" t="n">
         <v>4.85</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="T52" t="n">
         <v>2.25</v>
@@ -10669,115 +10669,115 @@
         <v>6</v>
       </c>
       <c r="V52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W52" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y52" t="n">
         <v>1.4</v>
       </c>
-      <c r="W52" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z52" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AD52" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AE52" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.82</v>
+        <v>3.12</v>
       </c>
       <c r="AH52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI52" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AQ52" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AS52" t="n">
         <v>2.05</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.4</v>
+        <v>3.87</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,16 +10848,16 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="R53" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="S53" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="T53" t="n">
         <v>2.25</v>
@@ -10866,115 +10866,115 @@
         <v>6</v>
       </c>
       <c r="V53" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="X53" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.12</v>
+        <v>3.82</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AI53" t="n">
-        <v>6.05</v>
+        <v>7.4</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AS53" t="n">
         <v>2.05</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.87</v>
+        <v>3.4</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4150,43 +4150,43 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X19" t="n">
         <v>2.3</v>
       </c>
-      <c r="U19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.29</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z19" t="n">
         <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
         <v>1.14</v>
@@ -4195,10 +4195,10 @@
         <v>4.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
         <v>2.43</v>
@@ -4207,22 +4207,22 @@
         <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BD19" t="n">
         <v>4.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
         <v>1.22</v>
@@ -6911,61 +6911,61 @@
         <v>1.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="S33" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T33" t="n">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="U33" t="n">
-        <v>7.39</v>
+        <v>6.81</v>
       </c>
       <c r="V33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W33" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="X33" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="AH33" t="n">
         <v>1.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.05</v>
+        <v>4.39</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.16</v>
@@ -7117,22 +7117,22 @@
         <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W34" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="X34" t="n">
         <v>2.59</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z34" t="n">
         <v>6</v>
@@ -7141,7 +7141,7 @@
         <v>1.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
         <v>1.23</v>
@@ -7150,10 +7150,10 @@
         <v>3.42</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG34" t="n">
         <v>2.92</v>
@@ -7162,19 +7162,19 @@
         <v>1.31</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.5</v>
+        <v>5.69</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.09</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN34" t="n">
         <v>1.48</v>
@@ -7183,46 +7183,46 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BB34" t="n">
         <v>1.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="BD34" t="n">
         <v>3.76</v>
@@ -7305,22 +7305,22 @@
         <v>3.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
         <v>1.96</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="T35" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="U35" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W35" t="n">
         <v>3.25</v>
@@ -7347,16 +7347,16 @@
         <v>4.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AG35" t="n">
         <v>2.62</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
         <v>4.85</v>
@@ -7383,31 +7383,31 @@
         <v>1.26</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AZ35" t="n">
         <v>2.33</v>
@@ -7422,7 +7422,7 @@
         <v>1.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="BE35" t="n">
         <v>1.8</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,88 +7499,88 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="U36" t="n">
-        <v>2.52</v>
+        <v>4.07</v>
       </c>
       <c r="V36" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="W36" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI36" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
         <v>2.38</v>
@@ -7592,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
         <v>1.5</v>
@@ -7607,25 +7607,25 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,88 +7696,88 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="S37" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="T37" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>4.07</v>
+        <v>2.52</v>
       </c>
       <c r="V37" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W37" t="n">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="X37" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA37" t="n">
         <v>1.01</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AI37" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR37" t="n">
         <v>2.38</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AW37" t="n">
         <v>1.5</v>
@@ -7804,25 +7804,25 @@
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="T40" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI40" t="n">
         <v>5.2</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W40" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>6.55</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AM40" t="n">
         <v>1.16</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.07</v>
+        <v>2.98</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>1.21</v>
       </c>
-      <c r="AQ40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BA40" t="n">
-        <v>5.59</v>
+        <v>5.53</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>8.119999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="S41" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="U41" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="X41" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB41" t="n">
         <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AI41" t="n">
         <v>5.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AN41" t="n">
-        <v>2.98</v>
+        <v>1.49</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.7</v>
+        <v>4.23</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.31</v>
+        <v>2</v>
       </c>
       <c r="BB41" t="n">
         <v>1.17</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="T42" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="V42" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W42" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="X42" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.95</v>
+        <v>6.7</v>
       </c>
       <c r="AA42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.23</v>
+        <v>3.56</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BB42" t="n">
         <v>1.2</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S43" t="n">
-        <v>3.04</v>
+        <v>3.38</v>
       </c>
       <c r="T43" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U43" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W43" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="X43" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.65</v>
+        <v>8.5</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1</v>
-      </c>
       <c r="AC43" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.67</v>
+        <v>2.68</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AF43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK43" t="n">
         <v>1.88</v>
       </c>
-      <c r="AG43" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AL43" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R44" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="S44" t="n">
-        <v>3.16</v>
+        <v>2.31</v>
       </c>
       <c r="T44" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U44" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W44" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="X44" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.05</v>
       </c>
-      <c r="AC44" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR44" t="n">
         <v>1.8</v>
       </c>
-      <c r="AM44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AS44" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.35</v>
+        <v>4.17</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.7</v>
+        <v>5.59</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9469,22 +9469,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q46" t="n">
         <v>4.6</v>
       </c>
       <c r="R46" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="S46" t="n">
         <v>1.92</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U46" t="n">
-        <v>5.75</v>
+        <v>4.84</v>
       </c>
       <c r="V46" t="n">
         <v>1.25</v>
@@ -9499,22 +9499,22 @@
         <v>1.58</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC46" t="n">
         <v>1.18</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF46" t="n">
         <v>2.27</v>
@@ -9526,37 +9526,37 @@
         <v>1.55</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AT46" t="n">
         <v>2.75</v>
@@ -9565,22 +9565,22 @@
         <v>3.84</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="BA46" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="BB46" t="n">
         <v>1.13</v>
@@ -10257,22 +10257,22 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="S50" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="T50" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="V50" t="n">
         <v>1.38</v>
@@ -10287,49 +10287,49 @@
         <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="AA50" t="n">
         <v>1.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC50" t="n">
         <v>1.29</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI50" t="n">
         <v>6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL50" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AM50" t="n">
         <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10338,13 +10338,13 @@
         <v>1.28</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AR50" t="n">
         <v>2.1</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AT50" t="n">
         <v>3.07</v>
@@ -10353,28 +10353,28 @@
         <v>3.18</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AY50" t="n">
         <v>1.32</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="BD50" t="n">
         <v>3.66</v>
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="Q51" t="n">
         <v>3.7</v>
       </c>
       <c r="R51" t="n">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="S51" t="n">
         <v>2.25</v>
@@ -10469,7 +10469,7 @@
         <v>2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="V51" t="n">
         <v>1.38</v>
@@ -10478,16 +10478,16 @@
         <v>2.81</v>
       </c>
       <c r="X51" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB51" t="n">
         <v>1.05</v>
@@ -10499,10 +10499,10 @@
         <v>3.6</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AG51" t="n">
         <v>2.85</v>
@@ -10517,13 +10517,13 @@
         <v>1.13</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN51" t="n">
         <v>2.05</v>
@@ -10532,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.55</v>
@@ -10547,7 +10547,7 @@
         <v>3.15</v>
       </c>
       <c r="AU51" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="AV51" t="n">
         <v>2.29</v>
@@ -10559,25 +10559,25 @@
         <v>1.49</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AZ51" t="n">
         <v>1.44</v>
       </c>
       <c r="BA51" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
         <v>1.18</v>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R52" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="S52" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="T52" t="n">
         <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="V52" t="n">
         <v>1.36</v>
@@ -10675,22 +10675,22 @@
         <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
         <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
         <v>3.4</v>
@@ -10699,13 +10699,13 @@
         <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI52" t="n">
         <v>6.05</v>
@@ -10717,13 +10717,13 @@
         <v>1.91</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AR52" t="n">
         <v>1.85</v>
@@ -10747,7 +10747,7 @@
         <v>3.75</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AW52" t="n">
         <v>2.09</v>
@@ -10762,13 +10762,13 @@
         <v>1.34</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="BB52" t="n">
         <v>1.25</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="BD52" t="n">
         <v>3.6</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="R53" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="S53" t="n">
         <v>2.19</v>
@@ -10863,31 +10863,31 @@
         <v>2.25</v>
       </c>
       <c r="U53" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="V53" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W53" t="n">
         <v>2.73</v>
       </c>
       <c r="X53" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="AA53" t="n">
         <v>1.02</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD53" t="n">
         <v>3</v>
@@ -10899,19 +10899,19 @@
         <v>1.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI53" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AJ53" t="n">
         <v>1.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AL53" t="n">
         <v>1.7</v>
@@ -10920,7 +10920,7 @@
         <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10935,13 +10935,13 @@
         <v>1.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AV53" t="n">
         <v>2.85</v>
@@ -10950,7 +10950,7 @@
         <v>2.15</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AY53" t="n">
         <v>1.46</v>
@@ -10959,13 +10959,13 @@
         <v>1.39</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="BB53" t="n">
         <v>1.3</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BD53" t="n">
         <v>3.2</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -804,28 +804,28 @@
         <v>3.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.26</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
         <v>3.25</v>
       </c>
       <c r="X2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Y2" t="n">
         <v>1.52</v>
@@ -846,31 +846,31 @@
         <v>4.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AG2" t="n">
         <v>2.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AN2" t="n">
         <v>1.21</v>
@@ -918,7 +918,7 @@
         <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BD2" t="n">
         <v>4.7</v>
@@ -998,37 +998,37 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
         <v>3.58</v>
       </c>
       <c r="X3" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA3" t="n">
         <v>1.15</v>
@@ -1040,22 +1040,22 @@
         <v>1.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.45</v>
+        <v>5.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH3" t="n">
         <v>1.68</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.26</v>
@@ -1064,7 +1064,7 @@
         <v>2.03</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AM3" t="n">
         <v>1.05</v>
@@ -1240,10 +1240,10 @@
         <v>2.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.07</v>
+        <v>2.37</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
         <v>3.6</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>3.42</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Y19" t="n">
         <v>1.54</v>
@@ -4195,10 +4195,10 @@
         <v>4.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG19" t="n">
         <v>2.43</v>
@@ -4207,7 +4207,7 @@
         <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.14</v>
@@ -4216,7 +4216,7 @@
         <v>1.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AM19" t="n">
         <v>1.21</v>
@@ -4228,40 +4228,40 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB19" t="n">
         <v>1.13</v>
@@ -4347,16 +4347,16 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="R20" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="S20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
         <v>2.45</v>
@@ -4368,7 +4368,7 @@
         <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="X20" t="n">
         <v>2.18</v>
@@ -4377,10 +4377,10 @@
         <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AB20" t="n">
         <v>1.02</v>
@@ -4392,10 +4392,10 @@
         <v>5.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AG20" t="n">
         <v>2.32</v>
@@ -4410,10 +4410,10 @@
         <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AM20" t="n">
         <v>1.15</v>
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="S21" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="T21" t="n">
         <v>2.15</v>
@@ -4562,16 +4562,16 @@
         <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="X21" t="n">
         <v>3.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
@@ -4580,13 +4580,13 @@
         <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AE21" t="n">
         <v>2.34</v>
@@ -4598,19 +4598,19 @@
         <v>4.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" t="n">
         <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4622,31 +4622,31 @@
         <v>1.17</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="AT21" t="n">
         <v>4.93</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AY21" t="n">
         <v>1.09</v>
@@ -4658,7 +4658,7 @@
         <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BC21" t="n">
         <v>2.47</v>
@@ -4667,7 +4667,7 @@
         <v>3.15</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BF21" t="n">
         <v>1.07</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5529,22 +5529,22 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6.01</v>
+        <v>6.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
         <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V26" t="n">
         <v>1.34</v>
@@ -5574,70 +5574,70 @@
         <v>3.72</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="AH26" t="n">
         <v>1.34</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.4</v>
+        <v>5.35</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AM26" t="n">
         <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BA26" t="n">
         <v>1.57</v>
@@ -5646,13 +5646,13 @@
         <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="BD26" t="n">
         <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BF26" t="n">
         <v>1.19</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.35</v>
       </c>
-      <c r="Q33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U33" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.24</v>
-      </c>
       <c r="W33" t="n">
-        <v>3.34</v>
+        <v>3.09</v>
       </c>
       <c r="X33" t="n">
-        <v>2.26</v>
+        <v>2.59</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.41</v>
+        <v>2.92</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.39</v>
+        <v>5.69</v>
       </c>
       <c r="AJ33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL34" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE34" t="n">
+      <c r="AM34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW34" t="n">
         <v>1.82</v>
       </c>
-      <c r="AF34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM34" t="n">
+      <c r="AX34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY34" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.76</v>
+        <v>4.35</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.96</v>
+        <v>6.5</v>
       </c>
       <c r="S35" t="n">
-        <v>3.82</v>
+        <v>1.78</v>
       </c>
       <c r="T35" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="U35" t="n">
-        <v>2.52</v>
+        <v>6.81</v>
       </c>
       <c r="V35" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W35" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="X35" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.85</v>
+        <v>4.39</v>
       </c>
       <c r="AJ35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM35" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY35" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ35" t="n">
-        <v>2.33</v>
+        <v>1.24</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="BB35" t="n">
         <v>1.14</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,88 +7499,88 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="S36" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="U36" t="n">
-        <v>4.07</v>
+        <v>2.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="W36" t="n">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="X36" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA36" t="n">
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI36" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR36" t="n">
         <v>2.38</v>
@@ -7592,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AW36" t="n">
         <v>1.5</v>
@@ -7607,25 +7607,25 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,88 +7696,88 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="R37" t="n">
-        <v>1.8</v>
+        <v>3.13</v>
       </c>
       <c r="S37" t="n">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="U37" t="n">
-        <v>2.52</v>
+        <v>4.34</v>
       </c>
       <c r="V37" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="W37" t="n">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA37" t="n">
         <v>1.01</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI37" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AM37" t="n">
         <v>1.28</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
         <v>2.38</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
         <v>1.5</v>
@@ -7804,25 +7804,25 @@
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="T38" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="X38" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AE38" t="n">
         <v>1.95</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.75</v>
+        <v>6.55</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AR38" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.55</v>
+        <v>2.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.85</v>
+        <v>4.17</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.12</v>
+        <v>2.83</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.54</v>
+        <v>5.59</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="R39" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="T39" t="n">
         <v>1.98</v>
       </c>
       <c r="U39" t="n">
-        <v>2.78</v>
+        <v>4.17</v>
       </c>
       <c r="V39" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W39" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="X39" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Y39" t="n">
         <v>1.32</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH39" t="n">
         <v>1.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>6.25</v>
+        <v>6.73</v>
       </c>
       <c r="AJ39" t="n">
         <v>1.03</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BF39" t="n">
         <v>1.11</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46092.69791666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,130 +8287,130 @@
         </is>
       </c>
       <c r="P40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN40" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U40" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W40" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y40" t="n">
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ40" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL40" t="n">
+      <c r="AR40" t="n">
         <v>1.7</v>
       </c>
-      <c r="AM40" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AS40" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.12</v>
+        <v>3.56</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.53</v>
+        <v>2.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BF40" t="n">
         <v>1.18</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="T41" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="X41" t="n">
-        <v>2.56</v>
+        <v>3.22</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.09</v>
+        <v>2.68</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.75</v>
+        <v>3.92</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="AU41" t="n">
-        <v>4.23</v>
+        <v>3.7</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="BA41" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,130 +8681,130 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="R42" t="n">
-        <v>2.45</v>
+        <v>7.5</v>
       </c>
       <c r="S42" t="n">
-        <v>3.54</v>
+        <v>1.85</v>
       </c>
       <c r="T42" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="U42" t="n">
-        <v>3.06</v>
+        <v>6.4</v>
       </c>
       <c r="V42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.39</v>
       </c>
-      <c r="W42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI42" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>2.98</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>1.21</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>2.05</v>
-      </c>
       <c r="BA42" t="n">
-        <v>2.2</v>
+        <v>5.53</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="BF42" t="n">
         <v>1.18</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,139 +8878,139 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="R43" t="n">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="S43" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="T43" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="U43" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="V43" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W43" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="X43" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z43" t="n">
         <v>8.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AD43" t="n">
         <v>2.68</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI43" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.84</v>
+        <v>3.07</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BB43" t="n">
         <v>1.3</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BD43" t="n">
         <v>3.22</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BH43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BI43" s="3" t="n">
         <v>46092.69791666666</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="S44" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="U44" t="n">
+        <v>3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI44" t="n">
         <v>5.2</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W44" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>6.55</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.06</v>
+        <v>1.49</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9156,52 +9156,52 @@
         <v>1.14</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.59</v>
+        <v>2</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="R45" t="n">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="S45" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="T45" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U45" t="n">
-        <v>4.05</v>
+        <v>4.84</v>
       </c>
       <c r="V45" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
         <v>3.42</v>
       </c>
       <c r="X45" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.45</v>
+        <v>4.9</v>
       </c>
       <c r="AA45" t="n">
         <v>1.12</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.94</v>
+        <v>2.66</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="AU45" t="n">
-        <v>2.95</v>
+        <v>3.84</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AY45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF45" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,37 +9469,37 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="S46" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="T46" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U46" t="n">
-        <v>4.84</v>
+        <v>4.05</v>
       </c>
       <c r="V46" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
         <v>3.42</v>
       </c>
       <c r="X46" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.9</v>
+        <v>5.45</v>
       </c>
       <c r="AA46" t="n">
         <v>1.12</v>
@@ -9508,94 +9508,94 @@
         <v>1.02</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AG46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL46" t="n">
         <v>2.4</v>
       </c>
-      <c r="AH46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AM46" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.58</v>
+        <v>2.24</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.75</v>
+        <v>3.02</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,40 +9666,40 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U47" t="n">
         <v>2.45</v>
       </c>
-      <c r="S47" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3</v>
-      </c>
       <c r="V47" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W47" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="X47" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB47" t="n">
         <v>1.01</v>
@@ -9711,7 +9711,7 @@
         <v>4.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF47" t="n">
         <v>2.35</v>
@@ -9723,67 +9723,67 @@
         <v>1.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AQ47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY47" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR47" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AZ47" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BD47" t="n">
         <v>4.85</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,43 +9863,43 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="S48" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="T48" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="U48" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W48" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="X48" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
         <v>1.16</v>
@@ -9908,79 +9908,79 @@
         <v>4.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AI48" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.43</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AW48" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="BB48" t="n">
         <v>1.16</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="BD48" t="n">
         <v>4.85</v>
@@ -9989,7 +9989,7 @@
         <v>1.98</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2377,28 +2377,28 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3.89</v>
+        <v>3.65</v>
       </c>
       <c r="S10" t="n">
         <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>4.98</v>
+        <v>4.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="X10" t="n">
         <v>2.67</v>
@@ -2416,10 +2416,10 @@
         <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="n">
         <v>1.84</v>
@@ -2428,28 +2428,28 @@
         <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AH10" t="n">
         <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2458,49 +2458,49 @@
         <v>1.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AW10" t="n">
         <v>1.84</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="BB10" t="n">
         <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
         <v>1.16</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,139 +4544,139 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
         <v>46092.60416666666</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL33" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE33" t="n">
+      <c r="AM33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW33" t="n">
         <v>1.82</v>
       </c>
-      <c r="AF33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="AX33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY33" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AZ33" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.76</v>
+        <v>4.35</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.96</v>
+        <v>6.5</v>
       </c>
       <c r="S34" t="n">
-        <v>3.82</v>
+        <v>1.78</v>
       </c>
       <c r="T34" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="U34" t="n">
-        <v>2.52</v>
+        <v>6.81</v>
       </c>
       <c r="V34" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="X34" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>4.85</v>
+        <v>4.39</v>
       </c>
       <c r="AJ34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM34" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY34" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>2.33</v>
+        <v>1.24</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="BB34" t="n">
         <v>1.14</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V35" t="n">
         <v>1.35</v>
       </c>
-      <c r="Q35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U35" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.24</v>
-      </c>
       <c r="W35" t="n">
-        <v>3.34</v>
+        <v>3.09</v>
       </c>
       <c r="X35" t="n">
-        <v>2.26</v>
+        <v>2.59</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AB35" t="n">
         <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.41</v>
+        <v>2.92</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.39</v>
+        <v>5.69</v>
       </c>
       <c r="AJ35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BF35" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.75</v>
+        <v>2.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="R38" t="n">
-        <v>4.6</v>
+        <v>2.21</v>
       </c>
       <c r="S38" t="n">
-        <v>2.31</v>
+        <v>3.26</v>
       </c>
       <c r="T38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR38" t="n">
         <v>2.1</v>
       </c>
-      <c r="U38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AE38" t="n">
+      <c r="AS38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA38" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF38" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>5.59</v>
-      </c>
       <c r="BB38" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46092.69791666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R40" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="S40" t="n">
-        <v>3.54</v>
+        <v>2.31</v>
       </c>
       <c r="T40" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U40" t="n">
-        <v>3.06</v>
+        <v>5.2</v>
       </c>
       <c r="V40" t="n">
         <v>1.39</v>
@@ -8311,109 +8311,109 @@
         <v>2.77</v>
       </c>
       <c r="X40" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AE40" t="n">
+      <c r="AK40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR40" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN40" t="n">
+      <c r="AS40" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>1.4</v>
       </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
+      <c r="BA40" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="BB40" t="n">
         <v>1.21</v>
       </c>
-      <c r="AQ40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BA40" t="n">
+      <c r="BC40" t="n">
         <v>2.2</v>
       </c>
-      <c r="BB40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BD40" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="R41" t="n">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
-        <v>3.38</v>
+        <v>1.85</v>
       </c>
       <c r="T41" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W41" t="n">
-        <v>2.41</v>
+        <v>3.04</v>
       </c>
       <c r="X41" t="n">
-        <v>3.22</v>
+        <v>2.59</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.92</v>
+        <v>3</v>
       </c>
       <c r="AH41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="BB41" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AW41" t="n">
+      <c r="BC41" t="n">
         <v>1.98</v>
       </c>
-      <c r="AX41" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD41" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>7.5</v>
+        <v>2.65</v>
       </c>
       <c r="S42" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="U42" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W42" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="X42" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB42" t="n">
         <v>1.01</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AG42" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI42" t="n">
         <v>5.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AN42" t="n">
-        <v>2.98</v>
+        <v>1.49</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.43</v>
+        <v>1.99</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.12</v>
+        <v>4.23</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.21</v>
+        <v>1.95</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.53</v>
+        <v>2</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,139 +8878,139 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT43" t="n">
         <v>2.95</v>
       </c>
-      <c r="R43" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.07</v>
-      </c>
       <c r="AU43" t="n">
-        <v>3.18</v>
+        <v>3.56</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BH43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
         <v>46092.69791666666</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="T44" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="X44" t="n">
-        <v>2.56</v>
+        <v>3.22</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.09</v>
+        <v>2.68</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.75</v>
+        <v>3.92</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AI44" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.23</v>
+        <v>3.7</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="BA44" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,37 +9272,37 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="S45" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="T45" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U45" t="n">
-        <v>4.84</v>
+        <v>4.05</v>
       </c>
       <c r="V45" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W45" t="n">
         <v>3.42</v>
       </c>
       <c r="X45" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.9</v>
+        <v>5.45</v>
       </c>
       <c r="AA45" t="n">
         <v>1.12</v>
@@ -9311,94 +9311,94 @@
         <v>1.02</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AG45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL45" t="n">
         <v>2.4</v>
       </c>
-      <c r="AH45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AM45" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.58</v>
+        <v>2.24</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AW45" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="BA45" t="n">
-        <v>4.75</v>
+        <v>3.02</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,37 +9469,37 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="R46" t="n">
-        <v>3.4</v>
+        <v>6.25</v>
       </c>
       <c r="S46" t="n">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="T46" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U46" t="n">
-        <v>4.05</v>
+        <v>4.84</v>
       </c>
       <c r="V46" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
         <v>3.42</v>
       </c>
       <c r="X46" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.45</v>
+        <v>4.9</v>
       </c>
       <c r="AA46" t="n">
         <v>1.12</v>
@@ -9508,94 +9508,94 @@
         <v>1.02</v>
       </c>
       <c r="AC46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>1.14</v>
       </c>
-      <c r="AD46" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW46" t="n">
+      <c r="BA46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC46" t="n">
         <v>1.78</v>
       </c>
-      <c r="AX46" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY46" t="n">
+      <c r="BD46" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF46" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-03-11.xlsx
+++ b/jogos_2026-03-11.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="X2" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="Z2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4.45</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.36</v>
+        <v>1.69</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>9.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.18</v>
       </c>
-      <c r="S3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="AD3" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1.21</v>
       </c>
-      <c r="W3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AN3" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>2.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
         <v>3.6</v>
@@ -1795,7 +1795,7 @@
         <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>5.37</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
         <v>2.1</v>
@@ -1804,10 +1804,10 @@
         <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X7" t="n">
         <v>2.9</v>
@@ -1816,7 +1816,7 @@
         <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
         <v>1.03</v>
@@ -1825,10 +1825,10 @@
         <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AE7" t="n">
         <v>1.96</v>
@@ -1855,7 +1855,7 @@
         <v>1.78</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AN7" t="n">
         <v>1.12</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,143 +3949,143 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
         <v>46092.54166666666</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,139 +4150,139 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U19" t="n">
         <v>3.75</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.12</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
         <v>46092.54166666666</v>
@@ -4347,28 +4347,28 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="S20" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="T20" t="n">
         <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>4.24</v>
+        <v>3.55</v>
       </c>
       <c r="V20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="X20" t="n">
         <v>2.18</v>
@@ -4401,25 +4401,25 @@
         <v>2.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AM20" t="n">
         <v>1.15</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,10 +4464,10 @@
         <v>1.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="BE20" t="n">
         <v>1.99</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,139 +4741,139 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
         <v>46092.60416666666</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,139 +5332,139 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI25" s="3" t="n">
         <v>46092.60416666666</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,88 +7499,88 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>2.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="R36" t="n">
-        <v>1.82</v>
+        <v>3.13</v>
       </c>
       <c r="S36" t="n">
-        <v>5.4</v>
+        <v>3.54</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="U36" t="n">
-        <v>2.5</v>
+        <v>4.34</v>
       </c>
       <c r="V36" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="W36" t="n">
-        <v>2.31</v>
+        <v>1.99</v>
       </c>
       <c r="X36" t="n">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA36" t="n">
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AC36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
         <v>2.38</v>
@@ -7592,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
         <v>1.5</v>
@@ -7607,25 +7607,25 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,88 +7696,88 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.59</v>
+        <v>4.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>3.13</v>
+        <v>1.82</v>
       </c>
       <c r="S37" t="n">
-        <v>3.54</v>
+        <v>5.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>4.34</v>
+        <v>2.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="W37" t="n">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="X37" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA37" t="n">
         <v>1.01</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AD37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK37" t="n">
         <v>2.14</v>
       </c>
-      <c r="AE37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AL37" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR37" t="n">
         <v>2.38</v>
@@ -7789,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AW37" t="n">
         <v>1.5</v>
@@ -7804,25 +7804,25 @@
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X39" t="n">
         <v>3.22</v>
       </c>
-      <c r="R39" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U39" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Y39" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA39" t="n">
         <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" t="n">
-        <v>6.73</v>
+        <v>7.5</v>
       </c>
       <c r="AJ39" t="n">
         <v>1.03</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AR39" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.54</v>
+        <v>1.89</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F40" t="in